--- a/backend/RNG_Report.xlsx
+++ b/backend/RNG_Report.xlsx
@@ -565,711 +565,711 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B2" t="n">
-        <v>92</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>217</v>
+        <v>82</v>
       </c>
       <c r="B4" t="n">
-        <v>207</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>246</v>
+        <v>45</v>
       </c>
       <c r="B5" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133</v>
+        <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>31</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>222</v>
+        <v>249</v>
       </c>
       <c r="B7" t="n">
-        <v>25</v>
+        <v>213</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>11</v>
+        <v>202</v>
       </c>
       <c r="B8" t="n">
-        <v>150</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>209</v>
+        <v>44</v>
       </c>
       <c r="B9" t="n">
-        <v>194</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>24</v>
+        <v>136</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>157</v>
+        <v>56</v>
       </c>
       <c r="B11" t="n">
-        <v>129</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134</v>
+        <v>48</v>
       </c>
       <c r="B12" t="n">
-        <v>115</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="B14" t="n">
-        <v>79</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B15" t="n">
-        <v>159</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>98</v>
+        <v>181</v>
       </c>
       <c r="B16" t="n">
-        <v>55</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="B17" t="n">
-        <v>179</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B18" t="n">
-        <v>93</v>
+        <v>239</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>8</v>
+        <v>226</v>
       </c>
       <c r="B19" t="n">
-        <v>138</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="B20" t="n">
-        <v>124</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="B21" t="n">
-        <v>104</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>24</v>
+        <v>206</v>
       </c>
       <c r="B22" t="n">
-        <v>145</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>173</v>
+        <v>97</v>
       </c>
       <c r="B23" t="n">
-        <v>15</v>
+        <v>229</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>36</v>
+        <v>152</v>
       </c>
       <c r="B24" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>73</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B26" t="n">
-        <v>234</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="B27" t="n">
-        <v>82</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>143</v>
+        <v>11</v>
       </c>
       <c r="B28" t="n">
-        <v>133</v>
+        <v>244</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>205</v>
+        <v>43</v>
       </c>
       <c r="B29" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B30" t="n">
-        <v>223</v>
+        <v>251</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="B31" t="n">
-        <v>191</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132</v>
+        <v>82</v>
       </c>
       <c r="B32" t="n">
-        <v>136</v>
+        <v>247</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="B33" t="n">
-        <v>205</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>136</v>
+        <v>191</v>
       </c>
       <c r="B34" t="n">
-        <v>184</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>213</v>
+        <v>49</v>
       </c>
       <c r="B35" t="n">
-        <v>94</v>
+        <v>140</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>81</v>
+        <v>211</v>
       </c>
       <c r="B36" t="n">
-        <v>161</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="B37" t="n">
-        <v>21</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121</v>
+        <v>180</v>
       </c>
       <c r="B38" t="n">
-        <v>223</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="B39" t="n">
-        <v>133</v>
+        <v>212</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="B40" t="n">
-        <v>135</v>
+        <v>230</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124</v>
+        <v>17</v>
       </c>
       <c r="B41" t="n">
-        <v>39</v>
+        <v>120</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="B42" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>146</v>
+        <v>193</v>
       </c>
       <c r="B43" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B44" t="n">
-        <v>34</v>
+        <v>178</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="B45" t="n">
-        <v>149</v>
+        <v>232</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>228</v>
+        <v>89</v>
       </c>
       <c r="B46" t="n">
-        <v>26</v>
+        <v>63</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>86</v>
+        <v>250</v>
       </c>
       <c r="B47" t="n">
-        <v>51</v>
+        <v>143</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>54</v>
+        <v>158</v>
       </c>
       <c r="B48" t="n">
-        <v>93</v>
+        <v>249</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>242</v>
+        <v>88</v>
       </c>
       <c r="B49" t="n">
-        <v>248</v>
+        <v>72</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>106</v>
+        <v>65</v>
       </c>
       <c r="B50" t="n">
-        <v>104</v>
+        <v>233</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B51" t="n">
-        <v>202</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>161</v>
+        <v>206</v>
       </c>
       <c r="B52" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>225</v>
+        <v>102</v>
       </c>
       <c r="B53" t="n">
-        <v>168</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>169</v>
+        <v>225</v>
       </c>
       <c r="B54" t="n">
-        <v>101</v>
+        <v>253</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>31</v>
+        <v>156</v>
       </c>
       <c r="B55" t="n">
-        <v>106</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="B56" t="n">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="B57" t="n">
-        <v>150</v>
+        <v>225</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>203</v>
+        <v>23</v>
       </c>
       <c r="B58" t="n">
-        <v>31</v>
+        <v>177</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="B59" t="n">
-        <v>98</v>
+        <v>191</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>115</v>
+        <v>66</v>
       </c>
       <c r="B60" t="n">
-        <v>6</v>
+        <v>162</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="B61" t="n">
-        <v>230</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>35</v>
+        <v>178</v>
       </c>
       <c r="B62" t="n">
-        <v>205</v>
+        <v>175</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>163</v>
+        <v>106</v>
       </c>
       <c r="B63" t="n">
-        <v>102</v>
+        <v>64</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125</v>
+        <v>194</v>
       </c>
       <c r="B64" t="n">
-        <v>123</v>
+        <v>178</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="B65" t="n">
-        <v>76</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>185</v>
+        <v>5</v>
       </c>
       <c r="B66" t="n">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>110</v>
+        <v>225</v>
       </c>
       <c r="B67" t="n">
-        <v>6</v>
+        <v>239</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126</v>
+        <v>228</v>
       </c>
       <c r="B68" t="n">
-        <v>176</v>
+        <v>168</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>21</v>
+        <v>241</v>
       </c>
       <c r="B69" t="n">
-        <v>120</v>
+        <v>253</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="B70" t="n">
-        <v>15</v>
+        <v>128</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="B71" t="n">
-        <v>47</v>
+        <v>166</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>46</v>
+        <v>191</v>
       </c>
       <c r="B72" t="n">
-        <v>88</v>
+        <v>105</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>28</v>
+        <v>160</v>
       </c>
       <c r="B73" t="n">
-        <v>136</v>
+        <v>212</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126</v>
+        <v>202</v>
       </c>
       <c r="B74" t="n">
-        <v>237</v>
+        <v>76</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="B75" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="B76" t="n">
-        <v>218</v>
+        <v>103</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>217</v>
+        <v>189</v>
       </c>
       <c r="B77" t="n">
-        <v>117</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>236</v>
+        <v>58</v>
       </c>
       <c r="B78" t="n">
-        <v>242</v>
+        <v>81</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>253</v>
+        <v>205</v>
       </c>
       <c r="B79" t="n">
-        <v>77</v>
+        <v>95</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B80" t="n">
-        <v>180</v>
+        <v>236</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>116</v>
+        <v>173</v>
       </c>
       <c r="B81" t="n">
-        <v>147</v>
+        <v>181</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>101</v>
+        <v>159</v>
       </c>
       <c r="B82" t="n">
-        <v>214</v>
+        <v>180</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="B83" t="n">
-        <v>87</v>
+        <v>8</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>254</v>
+        <v>71</v>
       </c>
       <c r="B84" t="n">
-        <v>206</v>
+        <v>189</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>219</v>
+        <v>23</v>
       </c>
       <c r="B85" t="n">
-        <v>145</v>
+        <v>89</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="B86" t="n">
-        <v>8</v>
+        <v>138</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="B87" t="n">
-        <v>83</v>
+        <v>133</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>235</v>
+        <v>70</v>
       </c>
       <c r="B88" t="n">
-        <v>150</v>
+        <v>44</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>212</v>
+        <v>101</v>
       </c>
       <c r="B89" t="n">
-        <v>81</v>
+        <v>29</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="B90" t="n">
         <v>58</v>
@@ -1277,1135 +1277,1135 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>188</v>
+        <v>11</v>
       </c>
       <c r="B91" t="n">
-        <v>115</v>
+        <v>81</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>116</v>
+        <v>51</v>
       </c>
       <c r="B92" t="n">
-        <v>238</v>
+        <v>99</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>117</v>
+        <v>240</v>
       </c>
       <c r="B93" t="n">
-        <v>255</v>
+        <v>193</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>210</v>
+        <v>102</v>
       </c>
       <c r="B94" t="n">
-        <v>86</v>
+        <v>209</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="B95" t="n">
-        <v>223</v>
+        <v>60</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>159</v>
+        <v>2</v>
       </c>
       <c r="B96" t="n">
-        <v>252</v>
+        <v>197</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="B97" t="n">
-        <v>252</v>
+        <v>107</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>36</v>
+        <v>214</v>
       </c>
       <c r="B98" t="n">
-        <v>112</v>
+        <v>252</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>15</v>
+        <v>193</v>
       </c>
       <c r="B99" t="n">
-        <v>83</v>
+        <v>189</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="B100" t="n">
-        <v>92</v>
+        <v>9</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>165</v>
+        <v>203</v>
       </c>
       <c r="B101" t="n">
-        <v>35</v>
+        <v>176</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>136</v>
+        <v>193</v>
       </c>
       <c r="B102" t="n">
-        <v>5</v>
+        <v>221</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>196</v>
+        <v>234</v>
       </c>
       <c r="B103" t="n">
-        <v>221</v>
+        <v>176</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="B104" t="n">
-        <v>169</v>
+        <v>107</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>47</v>
+        <v>113</v>
       </c>
       <c r="B105" t="n">
-        <v>142</v>
+        <v>58</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>231</v>
+        <v>141</v>
       </c>
       <c r="B106" t="n">
-        <v>49</v>
+        <v>152</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="B107" t="n">
-        <v>200</v>
+        <v>54</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>234</v>
+        <v>47</v>
       </c>
       <c r="B108" t="n">
-        <v>192</v>
+        <v>181</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>244</v>
+        <v>66</v>
       </c>
       <c r="B109" t="n">
-        <v>98</v>
+        <v>45</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="B110" t="n">
-        <v>89</v>
+        <v>164</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>248</v>
+        <v>56</v>
       </c>
       <c r="B111" t="n">
-        <v>76</v>
+        <v>46</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>205</v>
+        <v>239</v>
       </c>
       <c r="B112" t="n">
-        <v>128</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>179</v>
+        <v>99</v>
       </c>
       <c r="B113" t="n">
-        <v>221</v>
+        <v>162</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>162</v>
+        <v>198</v>
       </c>
       <c r="B114" t="n">
-        <v>61</v>
+        <v>167</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124</v>
+        <v>81</v>
       </c>
       <c r="B115" t="n">
-        <v>33</v>
+        <v>67</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>29</v>
+        <v>197</v>
       </c>
       <c r="B116" t="n">
-        <v>211</v>
+        <v>249</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="B117" t="n">
-        <v>32</v>
+        <v>188</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>255</v>
+        <v>143</v>
       </c>
       <c r="B118" t="n">
-        <v>137</v>
+        <v>83</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="B119" t="n">
-        <v>92</v>
+        <v>10</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="B120" t="n">
-        <v>23</v>
+        <v>226</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="B121" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>172</v>
+        <v>76</v>
       </c>
       <c r="B122" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>75</v>
+        <v>148</v>
       </c>
       <c r="B123" t="n">
-        <v>103</v>
+        <v>33</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="B124" t="n">
-        <v>158</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>51</v>
+        <v>237</v>
       </c>
       <c r="B125" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>115</v>
+        <v>205</v>
       </c>
       <c r="B126" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B127" t="n">
-        <v>252</v>
+        <v>201</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>58</v>
+        <v>199</v>
       </c>
       <c r="B128" t="n">
-        <v>119</v>
+        <v>103</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>67</v>
+        <v>177</v>
       </c>
       <c r="B129" t="n">
-        <v>180</v>
+        <v>162</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="B130" t="n">
-        <v>28</v>
+        <v>57</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="B131" t="n">
-        <v>107</v>
+        <v>158</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>201</v>
+        <v>126</v>
       </c>
       <c r="B132" t="n">
-        <v>54</v>
+        <v>207</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B133" t="n">
-        <v>138</v>
+        <v>222</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>159</v>
+        <v>123</v>
       </c>
       <c r="B134" t="n">
-        <v>225</v>
+        <v>162</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>19</v>
+        <v>132</v>
       </c>
       <c r="B135" t="n">
-        <v>13</v>
+        <v>169</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B136" t="n">
-        <v>85</v>
+        <v>147</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>71</v>
+        <v>238</v>
       </c>
       <c r="B137" t="n">
-        <v>195</v>
+        <v>163</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>50</v>
+        <v>170</v>
       </c>
       <c r="B138" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>145</v>
+        <v>85</v>
       </c>
       <c r="B139" t="n">
-        <v>223</v>
+        <v>66</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="B140" t="n">
-        <v>190</v>
+        <v>236</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>184</v>
+        <v>15</v>
       </c>
       <c r="B141" t="n">
-        <v>65</v>
+        <v>31</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="B142" t="n">
-        <v>106</v>
+        <v>85</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>56</v>
+        <v>134</v>
       </c>
       <c r="B143" t="n">
-        <v>227</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="B144" t="n">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>81</v>
+        <v>230</v>
       </c>
       <c r="B145" t="n">
-        <v>159</v>
+        <v>52</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>160</v>
+        <v>102</v>
       </c>
       <c r="B146" t="n">
-        <v>205</v>
+        <v>49</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="B147" t="n">
-        <v>21</v>
+        <v>141</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B148" t="n">
-        <v>223</v>
+        <v>163</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>236</v>
+        <v>11</v>
       </c>
       <c r="B149" t="n">
-        <v>173</v>
+        <v>208</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>160</v>
+        <v>10</v>
       </c>
       <c r="B150" t="n">
-        <v>12</v>
+        <v>219</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>221</v>
+        <v>107</v>
       </c>
       <c r="B151" t="n">
-        <v>188</v>
+        <v>129</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="B152" t="n">
-        <v>176</v>
+        <v>74</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>153</v>
+        <v>98</v>
       </c>
       <c r="B153" t="n">
-        <v>245</v>
+        <v>151</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="B154" t="n">
-        <v>19</v>
+        <v>106</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>185</v>
+        <v>28</v>
       </c>
       <c r="B155" t="n">
-        <v>42</v>
+        <v>71</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>34</v>
+        <v>144</v>
       </c>
       <c r="B156" t="n">
-        <v>178</v>
+        <v>44</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="B157" t="n">
-        <v>147</v>
+        <v>221</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="B158" t="n">
-        <v>82</v>
+        <v>170</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="B159" t="n">
-        <v>174</v>
+        <v>22</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="B160" t="n">
-        <v>227</v>
+        <v>80</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="B161" t="n">
-        <v>136</v>
+        <v>241</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="B162" t="n">
-        <v>162</v>
+        <v>187</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>47</v>
+        <v>156</v>
       </c>
       <c r="B163" t="n">
-        <v>238</v>
+        <v>8</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>158</v>
+        <v>214</v>
       </c>
       <c r="B164" t="n">
-        <v>143</v>
+        <v>6</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B165" t="n">
-        <v>2</v>
+        <v>202</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B166" t="n">
-        <v>165</v>
+        <v>107</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>118</v>
+        <v>223</v>
       </c>
       <c r="B167" t="n">
-        <v>248</v>
+        <v>49</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>98</v>
+        <v>147</v>
       </c>
       <c r="B168" t="n">
-        <v>39</v>
+        <v>248</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="B169" t="n">
-        <v>140</v>
+        <v>55</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>112</v>
+        <v>191</v>
       </c>
       <c r="B170" t="n">
-        <v>2</v>
+        <v>253</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="B171" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>84</v>
+        <v>216</v>
       </c>
       <c r="B172" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="B173" t="n">
-        <v>101</v>
+        <v>114</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B174" t="n">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>254</v>
+        <v>51</v>
       </c>
       <c r="B175" t="n">
-        <v>210</v>
+        <v>231</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>68</v>
+        <v>236</v>
       </c>
       <c r="B176" t="n">
-        <v>216</v>
+        <v>234</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="B177" t="n">
-        <v>192</v>
+        <v>60</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>97</v>
+        <v>4</v>
       </c>
       <c r="B178" t="n">
-        <v>49</v>
+        <v>185</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127</v>
+        <v>165</v>
       </c>
       <c r="B179" t="n">
-        <v>92</v>
+        <v>207</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="B180" t="n">
-        <v>195</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>148</v>
+        <v>95</v>
       </c>
       <c r="B181" t="n">
-        <v>226</v>
+        <v>83</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>62</v>
+        <v>195</v>
       </c>
       <c r="B182" t="n">
-        <v>126</v>
+        <v>251</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="B183" t="n">
-        <v>31</v>
+        <v>214</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>224</v>
+        <v>17</v>
       </c>
       <c r="B184" t="n">
-        <v>38</v>
+        <v>168</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>165</v>
+        <v>215</v>
       </c>
       <c r="B185" t="n">
-        <v>116</v>
+        <v>13</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>77</v>
+        <v>171</v>
       </c>
       <c r="B186" t="n">
-        <v>147</v>
+        <v>118</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>194</v>
+        <v>167</v>
       </c>
       <c r="B187" t="n">
-        <v>190</v>
+        <v>177</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>101</v>
+        <v>254</v>
       </c>
       <c r="B188" t="n">
-        <v>38</v>
+        <v>81</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="B189" t="n">
-        <v>49</v>
+        <v>86</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="B190" t="n">
-        <v>21</v>
+        <v>233</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B191" t="n">
-        <v>124</v>
+        <v>206</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>83</v>
+        <v>174</v>
       </c>
       <c r="B192" t="n">
-        <v>196</v>
+        <v>70</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>182</v>
+        <v>243</v>
       </c>
       <c r="B193" t="n">
-        <v>184</v>
+        <v>59</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>207</v>
+        <v>79</v>
       </c>
       <c r="B194" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>136</v>
+        <v>186</v>
       </c>
       <c r="B195" t="n">
-        <v>187</v>
+        <v>63</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>229</v>
+        <v>150</v>
       </c>
       <c r="B196" t="n">
-        <v>138</v>
+        <v>254</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>233</v>
+        <v>143</v>
       </c>
       <c r="B197" t="n">
-        <v>187</v>
+        <v>214</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="B198" t="n">
-        <v>39</v>
+        <v>168</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="B199" t="n">
-        <v>223</v>
+        <v>111</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>230</v>
+        <v>254</v>
       </c>
       <c r="B200" t="n">
-        <v>121</v>
+        <v>151</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>189</v>
+        <v>13</v>
       </c>
       <c r="B201" t="n">
-        <v>155</v>
+        <v>139</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="B202" t="n">
-        <v>182</v>
+        <v>160</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>101</v>
+        <v>61</v>
       </c>
       <c r="B203" t="n">
-        <v>253</v>
+        <v>224</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="B204" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B205" t="n">
-        <v>89</v>
+        <v>140</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="B206" t="n">
-        <v>223</v>
+        <v>185</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>203</v>
+        <v>48</v>
       </c>
       <c r="B207" t="n">
-        <v>114</v>
+        <v>24</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="B208" t="n">
-        <v>143</v>
+        <v>123</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>61</v>
+        <v>212</v>
       </c>
       <c r="B209" t="n">
-        <v>198</v>
+        <v>62</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>203</v>
+        <v>112</v>
       </c>
       <c r="B210" t="n">
-        <v>143</v>
+        <v>7</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>134</v>
+        <v>30</v>
       </c>
       <c r="B211" t="n">
-        <v>255</v>
+        <v>90</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>177</v>
+        <v>2</v>
       </c>
       <c r="B212" t="n">
-        <v>252</v>
+        <v>96</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>210</v>
+        <v>124</v>
       </c>
       <c r="B213" t="n">
-        <v>148</v>
+        <v>204</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>57</v>
+        <v>209</v>
       </c>
       <c r="B214" t="n">
-        <v>254</v>
+        <v>39</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B215" t="n">
-        <v>90</v>
+        <v>162</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="B216" t="n">
-        <v>199</v>
+        <v>231</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="B217" t="n">
-        <v>42</v>
+        <v>159</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>195</v>
+        <v>81</v>
       </c>
       <c r="B218" t="n">
-        <v>248</v>
+        <v>12</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="B219" t="n">
-        <v>245</v>
+        <v>19</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="B220" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>103</v>
+        <v>153</v>
       </c>
       <c r="B221" t="n">
-        <v>28</v>
+        <v>155</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="B222" t="n">
-        <v>134</v>
+        <v>168</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>194</v>
+        <v>242</v>
       </c>
       <c r="B223" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>178</v>
+        <v>117</v>
       </c>
       <c r="B224" t="n">
-        <v>152</v>
+        <v>228</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>156</v>
+        <v>188</v>
       </c>
       <c r="B225" t="n">
-        <v>245</v>
+        <v>210</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>219</v>
+        <v>110</v>
       </c>
       <c r="B226" t="n">
-        <v>251</v>
+        <v>187</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>121</v>
+        <v>47</v>
       </c>
       <c r="B227" t="n">
-        <v>213</v>
+        <v>224</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>126</v>
+        <v>33</v>
       </c>
       <c r="B228" t="n">
-        <v>211</v>
+        <v>226</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>26</v>
+        <v>144</v>
       </c>
       <c r="B229" t="n">
-        <v>172</v>
+        <v>153</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>191</v>
+        <v>252</v>
       </c>
       <c r="B230" t="n">
-        <v>208</v>
+        <v>164</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>26</v>
+        <v>142</v>
       </c>
       <c r="B231" t="n">
-        <v>181</v>
+        <v>249</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>32</v>
+        <v>189</v>
       </c>
       <c r="B232" t="n">
         <v>11</v>
@@ -2413,2154 +2413,2154 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>82</v>
+        <v>193</v>
       </c>
       <c r="B233" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>16</v>
+        <v>234</v>
       </c>
       <c r="B234" t="n">
-        <v>238</v>
+        <v>91</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>40</v>
+        <v>124</v>
       </c>
       <c r="B235" t="n">
-        <v>26</v>
+        <v>225</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>30</v>
+        <v>170</v>
       </c>
       <c r="B236" t="n">
-        <v>43</v>
+        <v>202</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B237" t="n">
-        <v>102</v>
+        <v>52</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>189</v>
+        <v>35</v>
       </c>
       <c r="B238" t="n">
-        <v>124</v>
+        <v>85</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="B239" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="B240" t="n">
-        <v>23</v>
+        <v>193</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>218</v>
+        <v>135</v>
       </c>
       <c r="B241" t="n">
-        <v>247</v>
+        <v>85</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>17</v>
+        <v>155</v>
       </c>
       <c r="B242" t="n">
-        <v>46</v>
+        <v>135</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>53</v>
+        <v>197</v>
       </c>
       <c r="B243" t="n">
-        <v>83</v>
+        <v>187</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>97</v>
+        <v>213</v>
       </c>
       <c r="B244" t="n">
-        <v>108</v>
+        <v>179</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>247</v>
+        <v>126</v>
       </c>
       <c r="B245" t="n">
-        <v>106</v>
+        <v>129</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>36</v>
+        <v>144</v>
       </c>
       <c r="B246" t="n">
-        <v>102</v>
+        <v>201</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B247" t="n">
-        <v>206</v>
+        <v>182</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>72</v>
+        <v>250</v>
       </c>
       <c r="B248" t="n">
-        <v>166</v>
+        <v>36</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="B249" t="n">
-        <v>8</v>
+        <v>93</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>193</v>
+        <v>75</v>
       </c>
       <c r="B250" t="n">
-        <v>57</v>
+        <v>81</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>240</v>
+        <v>70</v>
       </c>
       <c r="B251" t="n">
-        <v>205</v>
+        <v>236</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>118</v>
+        <v>202</v>
       </c>
       <c r="B252" t="n">
-        <v>224</v>
+        <v>28</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>235</v>
+        <v>48</v>
       </c>
       <c r="B253" t="n">
-        <v>121</v>
+        <v>156</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>203</v>
+        <v>145</v>
       </c>
       <c r="B254" t="n">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="B255" t="n">
-        <v>138</v>
+        <v>4</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>115</v>
+        <v>36</v>
       </c>
       <c r="B256" t="n">
-        <v>211</v>
+        <v>44</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>91</v>
+        <v>219</v>
       </c>
       <c r="B257" t="n">
-        <v>143</v>
+        <v>120</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="B258" t="n">
-        <v>110</v>
+        <v>98</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="B259" t="n">
-        <v>240</v>
+        <v>174</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="B260" t="n">
-        <v>205</v>
+        <v>82</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>255</v>
+        <v>123</v>
       </c>
       <c r="B261" t="n">
-        <v>254</v>
+        <v>75</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="B262" t="n">
-        <v>150</v>
+        <v>249</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>227</v>
+        <v>113</v>
       </c>
       <c r="B263" t="n">
-        <v>208</v>
+        <v>183</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>35</v>
+        <v>144</v>
       </c>
       <c r="B264" t="n">
-        <v>176</v>
+        <v>108</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="B265" t="n">
-        <v>178</v>
+        <v>232</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>252</v>
+        <v>209</v>
       </c>
       <c r="B266" t="n">
-        <v>144</v>
+        <v>204</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>199</v>
+        <v>114</v>
       </c>
       <c r="B267" t="n">
-        <v>3</v>
+        <v>66</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>208</v>
+        <v>27</v>
       </c>
       <c r="B268" t="n">
-        <v>32</v>
+        <v>98</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="B269" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>210</v>
+        <v>87</v>
       </c>
       <c r="B270" t="n">
-        <v>32</v>
+        <v>154</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>56</v>
+        <v>180</v>
       </c>
       <c r="B271" t="n">
-        <v>54</v>
+        <v>149</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>188</v>
+        <v>59</v>
       </c>
       <c r="B272" t="n">
-        <v>122</v>
+        <v>13</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>49</v>
+        <v>127</v>
       </c>
       <c r="B273" t="n">
-        <v>130</v>
+        <v>184</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="B274" t="n">
-        <v>219</v>
+        <v>88</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>44</v>
+        <v>141</v>
       </c>
       <c r="B275" t="n">
-        <v>119</v>
+        <v>102</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
+        <v>170</v>
+      </c>
+      <c r="B276" t="n">
         <v>98</v>
-      </c>
-      <c r="B276" t="n">
-        <v>81</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="B277" t="n">
-        <v>254</v>
+        <v>30</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>116</v>
+        <v>212</v>
       </c>
       <c r="B278" t="n">
-        <v>157</v>
+        <v>189</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>151</v>
+        <v>8</v>
       </c>
       <c r="B279" t="n">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="B280" t="n">
-        <v>151</v>
+        <v>116</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>31</v>
+        <v>144</v>
       </c>
       <c r="B281" t="n">
-        <v>255</v>
+        <v>68</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>151</v>
+        <v>19</v>
       </c>
       <c r="B282" t="n">
-        <v>13</v>
+        <v>108</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B283" t="n">
-        <v>14</v>
+        <v>245</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>223</v>
+        <v>155</v>
       </c>
       <c r="B284" t="n">
-        <v>186</v>
+        <v>79</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="B285" t="n">
-        <v>22</v>
+        <v>216</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>136</v>
+        <v>72</v>
       </c>
       <c r="B286" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="B287" t="n">
-        <v>146</v>
+        <v>122</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="B288" t="n">
-        <v>31</v>
+        <v>61</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>35</v>
+        <v>243</v>
       </c>
       <c r="B289" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>75</v>
+        <v>192</v>
       </c>
       <c r="B290" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>177</v>
+        <v>36</v>
       </c>
       <c r="B291" t="n">
-        <v>191</v>
+        <v>45</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>24</v>
+        <v>182</v>
       </c>
       <c r="B292" t="n">
-        <v>215</v>
+        <v>237</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="B293" t="n">
-        <v>174</v>
+        <v>131</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="B294" t="n">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="B295" t="n">
-        <v>36</v>
+        <v>106</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>247</v>
+        <v>40</v>
       </c>
       <c r="B296" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="B297" t="n">
-        <v>158</v>
+        <v>207</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>251</v>
+        <v>41</v>
       </c>
       <c r="B298" t="n">
-        <v>84</v>
+        <v>21</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>147</v>
+        <v>10</v>
       </c>
       <c r="B299" t="n">
-        <v>239</v>
+        <v>127</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>106</v>
+        <v>151</v>
       </c>
       <c r="B300" t="n">
-        <v>90</v>
+        <v>31</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="B301" t="n">
-        <v>187</v>
+        <v>66</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>116</v>
+        <v>14</v>
       </c>
       <c r="B302" t="n">
-        <v>134</v>
+        <v>231</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B303" t="n">
-        <v>171</v>
+        <v>152</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="B304" t="n">
-        <v>213</v>
+        <v>83</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>118</v>
+        <v>174</v>
       </c>
       <c r="B305" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>234</v>
+        <v>54</v>
       </c>
       <c r="B306" t="n">
-        <v>151</v>
+        <v>209</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="B307" t="n">
-        <v>4</v>
+        <v>113</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="B308" t="n">
-        <v>209</v>
+        <v>201</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B309" t="n">
-        <v>210</v>
+        <v>99</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>86</v>
+        <v>201</v>
       </c>
       <c r="B310" t="n">
-        <v>153</v>
+        <v>207</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>62</v>
+        <v>115</v>
       </c>
       <c r="B311" t="n">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="B312" t="n">
-        <v>110</v>
+        <v>166</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>133</v>
+        <v>202</v>
       </c>
       <c r="B313" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>5</v>
+        <v>186</v>
       </c>
       <c r="B314" t="n">
-        <v>206</v>
+        <v>62</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>11</v>
+        <v>241</v>
       </c>
       <c r="B315" t="n">
-        <v>210</v>
+        <v>217</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B316" t="n">
-        <v>138</v>
+        <v>124</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>149</v>
+        <v>8</v>
       </c>
       <c r="B317" t="n">
-        <v>183</v>
+        <v>85</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="B318" t="n">
-        <v>170</v>
+        <v>254</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>251</v>
+        <v>67</v>
       </c>
       <c r="B319" t="n">
-        <v>103</v>
+        <v>188</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>140</v>
+        <v>225</v>
       </c>
       <c r="B320" t="n">
-        <v>204</v>
+        <v>5</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="B321" t="n">
-        <v>191</v>
+        <v>202</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>84</v>
+        <v>184</v>
       </c>
       <c r="B322" t="n">
-        <v>233</v>
+        <v>28</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>246</v>
+        <v>73</v>
       </c>
       <c r="B323" t="n">
-        <v>75</v>
+        <v>180</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>247</v>
+        <v>177</v>
       </c>
       <c r="B324" t="n">
-        <v>250</v>
+        <v>87</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="B325" t="n">
-        <v>249</v>
+        <v>74</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B326" t="n">
-        <v>109</v>
+        <v>138</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="B327" t="n">
-        <v>49</v>
+        <v>102</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>234</v>
+        <v>154</v>
       </c>
       <c r="B328" t="n">
-        <v>173</v>
+        <v>128</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="B329" t="n">
-        <v>129</v>
+        <v>192</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>10</v>
+        <v>164</v>
       </c>
       <c r="B330" t="n">
-        <v>41</v>
+        <v>81</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="B331" t="n">
-        <v>139</v>
+        <v>90</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B332" t="n">
-        <v>4</v>
+        <v>155</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="B333" t="n">
-        <v>120</v>
+        <v>5</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>55</v>
+        <v>195</v>
       </c>
       <c r="B334" t="n">
-        <v>248</v>
+        <v>83</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>169</v>
+        <v>37</v>
       </c>
       <c r="B335" t="n">
-        <v>223</v>
+        <v>163</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>44</v>
+        <v>129</v>
       </c>
       <c r="B336" t="n">
-        <v>150</v>
+        <v>33</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>76</v>
+        <v>230</v>
       </c>
       <c r="B337" t="n">
-        <v>52</v>
+        <v>22</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>12</v>
+        <v>255</v>
       </c>
       <c r="B338" t="n">
-        <v>198</v>
+        <v>210</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>233</v>
+        <v>133</v>
       </c>
       <c r="B339" t="n">
-        <v>90</v>
+        <v>25</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="B340" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>172</v>
+        <v>125</v>
       </c>
       <c r="B341" t="n">
-        <v>99</v>
+        <v>217</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>54</v>
+        <v>186</v>
       </c>
       <c r="B342" t="n">
-        <v>42</v>
+        <v>227</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B343" t="n">
-        <v>238</v>
+        <v>139</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>151</v>
+        <v>72</v>
       </c>
       <c r="B344" t="n">
-        <v>234</v>
+        <v>101</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>25</v>
+        <v>219</v>
       </c>
       <c r="B345" t="n">
-        <v>22</v>
+        <v>75</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>201</v>
+        <v>92</v>
       </c>
       <c r="B346" t="n">
-        <v>174</v>
+        <v>210</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="B347" t="n">
-        <v>95</v>
+        <v>107</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="B348" t="n">
-        <v>173</v>
+        <v>237</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="B349" t="n">
-        <v>37</v>
+        <v>83</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>169</v>
+        <v>90</v>
       </c>
       <c r="B350" t="n">
-        <v>7</v>
+        <v>250</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>123</v>
+        <v>45</v>
       </c>
       <c r="B351" t="n">
-        <v>215</v>
+        <v>138</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>255</v>
+        <v>183</v>
       </c>
       <c r="B352" t="n">
-        <v>225</v>
+        <v>198</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>105</v>
+        <v>61</v>
       </c>
       <c r="B353" t="n">
-        <v>97</v>
+        <v>5</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="B354" t="n">
-        <v>222</v>
+        <v>236</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="B355" t="n">
-        <v>48</v>
+        <v>114</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>14</v>
+        <v>118</v>
       </c>
       <c r="B356" t="n">
-        <v>81</v>
+        <v>47</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>154</v>
+        <v>222</v>
       </c>
       <c r="B357" t="n">
-        <v>217</v>
+        <v>124</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="B358" t="n">
-        <v>36</v>
+        <v>162</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="B359" t="n">
-        <v>247</v>
+        <v>75</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>58</v>
+        <v>177</v>
       </c>
       <c r="B360" t="n">
-        <v>182</v>
+        <v>251</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="B361" t="n">
-        <v>180</v>
+        <v>212</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>230</v>
+        <v>152</v>
       </c>
       <c r="B362" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="B363" t="n">
-        <v>194</v>
+        <v>242</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="B364" t="n">
-        <v>184</v>
+        <v>135</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>11</v>
+        <v>208</v>
       </c>
       <c r="B365" t="n">
-        <v>147</v>
+        <v>46</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>249</v>
+        <v>60</v>
       </c>
       <c r="B366" t="n">
-        <v>131</v>
+        <v>190</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B367" t="n">
-        <v>35</v>
+        <v>248</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="B368" t="n">
-        <v>177</v>
+        <v>132</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>136</v>
+        <v>38</v>
       </c>
       <c r="B369" t="n">
-        <v>222</v>
+        <v>92</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>56</v>
+        <v>223</v>
       </c>
       <c r="B370" t="n">
-        <v>42</v>
+        <v>147</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>48</v>
+        <v>249</v>
       </c>
       <c r="B371" t="n">
-        <v>14</v>
+        <v>254</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B372" t="n">
-        <v>237</v>
+        <v>40</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="B373" t="n">
-        <v>137</v>
+        <v>93</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="B374" t="n">
-        <v>90</v>
+        <v>131</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>181</v>
+        <v>139</v>
       </c>
       <c r="B375" t="n">
-        <v>142</v>
+        <v>10</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>48</v>
+        <v>181</v>
       </c>
       <c r="B376" t="n">
-        <v>252</v>
+        <v>120</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="B377" t="n">
-        <v>2</v>
+        <v>104</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="B378" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>208</v>
+        <v>132</v>
       </c>
       <c r="B379" t="n">
-        <v>89</v>
+        <v>35</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>210</v>
+        <v>45</v>
       </c>
       <c r="B380" t="n">
-        <v>134</v>
+        <v>184</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>206</v>
+        <v>16</v>
       </c>
       <c r="B381" t="n">
-        <v>157</v>
+        <v>147</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="B382" t="n">
-        <v>170</v>
+        <v>7</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B383" t="n">
-        <v>15</v>
+        <v>126</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="B384" t="n">
-        <v>180</v>
+        <v>99</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>194</v>
+        <v>64</v>
       </c>
       <c r="B385" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B386" t="n">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B387" t="n">
-        <v>175</v>
+        <v>149</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>43</v>
+        <v>102</v>
       </c>
       <c r="B388" t="n">
-        <v>114</v>
+        <v>193</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>106</v>
+        <v>247</v>
       </c>
       <c r="B389" t="n">
-        <v>30</v>
+        <v>93</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>148</v>
+        <v>71</v>
       </c>
       <c r="B390" t="n">
-        <v>96</v>
+        <v>5</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B391" t="n">
-        <v>156</v>
+        <v>67</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>232</v>
+        <v>201</v>
       </c>
       <c r="B392" t="n">
-        <v>250</v>
+        <v>13</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>191</v>
+        <v>151</v>
       </c>
       <c r="B393" t="n">
-        <v>243</v>
+        <v>178</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B394" t="n">
-        <v>11</v>
+        <v>75</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B395" t="n">
-        <v>96</v>
+        <v>213</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="B396" t="n">
-        <v>110</v>
+        <v>170</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="B397" t="n">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>31</v>
+        <v>243</v>
       </c>
       <c r="B398" t="n">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="B399" t="n">
-        <v>176</v>
+        <v>113</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="B400" t="n">
-        <v>98</v>
+        <v>243</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>177</v>
+        <v>237</v>
       </c>
       <c r="B401" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>193</v>
+        <v>156</v>
       </c>
       <c r="B402" t="n">
-        <v>242</v>
+        <v>214</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>6</v>
+        <v>207</v>
       </c>
       <c r="B403" t="n">
-        <v>23</v>
+        <v>108</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>75</v>
+        <v>201</v>
       </c>
       <c r="B404" t="n">
-        <v>41</v>
+        <v>128</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>89</v>
+        <v>207</v>
       </c>
       <c r="B405" t="n">
-        <v>144</v>
+        <v>86</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>250</v>
+        <v>119</v>
       </c>
       <c r="B406" t="n">
-        <v>5</v>
+        <v>74</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>158</v>
+        <v>11</v>
       </c>
       <c r="B407" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="B408" t="n">
-        <v>24</v>
+        <v>154</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B409" t="n">
-        <v>252</v>
+        <v>115</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>238</v>
+        <v>76</v>
       </c>
       <c r="B410" t="n">
-        <v>52</v>
+        <v>171</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>206</v>
+        <v>43</v>
       </c>
       <c r="B411" t="n">
-        <v>166</v>
+        <v>59</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>102</v>
+        <v>237</v>
       </c>
       <c r="B412" t="n">
-        <v>215</v>
+        <v>188</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="B413" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="B414" t="n">
-        <v>99</v>
+        <v>17</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>108</v>
+        <v>168</v>
       </c>
       <c r="B415" t="n">
-        <v>15</v>
+        <v>80</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>32</v>
+        <v>205</v>
       </c>
       <c r="B416" t="n">
-        <v>160</v>
+        <v>37</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>23</v>
+        <v>253</v>
       </c>
       <c r="B417" t="n">
-        <v>112</v>
+        <v>240</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>203</v>
+        <v>45</v>
       </c>
       <c r="B418" t="n">
-        <v>100</v>
+        <v>209</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>66</v>
+        <v>188</v>
       </c>
       <c r="B419" t="n">
-        <v>132</v>
+        <v>219</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="B420" t="n">
-        <v>83</v>
+        <v>42</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>178</v>
+        <v>123</v>
       </c>
       <c r="B421" t="n">
-        <v>226</v>
+        <v>255</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>106</v>
+        <v>58</v>
       </c>
       <c r="B422" t="n">
-        <v>253</v>
+        <v>233</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>194</v>
+        <v>70</v>
       </c>
       <c r="B423" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="B424" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>5</v>
+        <v>99</v>
       </c>
       <c r="B425" t="n">
-        <v>232</v>
+        <v>80</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>225</v>
+        <v>126</v>
       </c>
       <c r="B426" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>228</v>
+        <v>152</v>
       </c>
       <c r="B427" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>241</v>
+        <v>161</v>
       </c>
       <c r="B428" t="n">
-        <v>197</v>
+        <v>173</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="B429" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>103</v>
+        <v>176</v>
       </c>
       <c r="B430" t="n">
-        <v>135</v>
+        <v>89</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>191</v>
+        <v>8</v>
       </c>
       <c r="B431" t="n">
-        <v>185</v>
+        <v>111</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>160</v>
+        <v>114</v>
       </c>
       <c r="B432" t="n">
-        <v>105</v>
+        <v>149</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>202</v>
+        <v>144</v>
       </c>
       <c r="B433" t="n">
-        <v>31</v>
+        <v>70</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>98</v>
+        <v>5</v>
       </c>
       <c r="B434" t="n">
-        <v>20</v>
+        <v>124</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>72</v>
+        <v>154</v>
       </c>
       <c r="B435" t="n">
-        <v>38</v>
+        <v>156</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>189</v>
+        <v>60</v>
       </c>
       <c r="B436" t="n">
-        <v>138</v>
+        <v>209</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>58</v>
+        <v>166</v>
       </c>
       <c r="B437" t="n">
-        <v>61</v>
+        <v>134</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>205</v>
+        <v>243</v>
       </c>
       <c r="B438" t="n">
-        <v>90</v>
+        <v>247</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B439" t="n">
-        <v>39</v>
+        <v>250</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B440" t="n">
-        <v>226</v>
+        <v>55</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="B441" t="n">
-        <v>253</v>
+        <v>186</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="B442" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>71</v>
+        <v>208</v>
       </c>
       <c r="B443" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>23</v>
+        <v>242</v>
       </c>
       <c r="B444" t="n">
-        <v>128</v>
+        <v>144</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>6</v>
+        <v>249</v>
       </c>
       <c r="B445" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>141</v>
+        <v>229</v>
       </c>
       <c r="B446" t="n">
-        <v>108</v>
+        <v>95</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>70</v>
+        <v>236</v>
       </c>
       <c r="B447" t="n">
-        <v>10</v>
+        <v>146</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="B448" t="n">
-        <v>220</v>
+        <v>26</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="B449" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="B450" t="n">
-        <v>193</v>
+        <v>19</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="B451" t="n">
-        <v>251</v>
+        <v>241</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B452" t="n">
-        <v>226</v>
+        <v>126</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="B453" t="n">
-        <v>226</v>
+        <v>142</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>43</v>
+        <v>169</v>
       </c>
       <c r="B454" t="n">
-        <v>206</v>
+        <v>100</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>2</v>
+        <v>220</v>
       </c>
       <c r="B455" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="B456" t="n">
-        <v>172</v>
+        <v>239</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>214</v>
+        <v>126</v>
       </c>
       <c r="B457" t="n">
-        <v>167</v>
+        <v>28</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>193</v>
+        <v>146</v>
       </c>
       <c r="B458" t="n">
-        <v>74</v>
+        <v>180</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>23</v>
+        <v>167</v>
       </c>
       <c r="B459" t="n">
-        <v>227</v>
+        <v>30</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>203</v>
+        <v>100</v>
       </c>
       <c r="B460" t="n">
-        <v>91</v>
+        <v>68</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>193</v>
+        <v>9</v>
       </c>
       <c r="B461" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>234</v>
+        <v>39</v>
       </c>
       <c r="B462" t="n">
-        <v>135</v>
+        <v>54</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>166</v>
+        <v>245</v>
       </c>
       <c r="B463" t="n">
-        <v>97</v>
+        <v>37</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>113</v>
+        <v>33</v>
       </c>
       <c r="B464" t="n">
-        <v>167</v>
+        <v>106</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>141</v>
+        <v>244</v>
       </c>
       <c r="B465" t="n">
-        <v>154</v>
+        <v>87</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>185</v>
+        <v>3</v>
       </c>
       <c r="B466" t="n">
-        <v>211</v>
+        <v>49</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>47</v>
+        <v>133</v>
       </c>
       <c r="B467" t="n">
-        <v>231</v>
+        <v>70</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B468" t="n">
-        <v>225</v>
+        <v>185</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>2</v>
+        <v>242</v>
       </c>
       <c r="B469" t="n">
-        <v>155</v>
+        <v>28</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B470" t="n">
-        <v>130</v>
+        <v>48</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>239</v>
+        <v>5</v>
       </c>
       <c r="B471" t="n">
-        <v>209</v>
+        <v>49</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="B472" t="n">
-        <v>205</v>
+        <v>75</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>198</v>
+        <v>243</v>
       </c>
       <c r="B473" t="n">
-        <v>72</v>
+        <v>27</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="B474" t="n">
-        <v>218</v>
+        <v>131</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>197</v>
+        <v>89</v>
       </c>
       <c r="B475" t="n">
-        <v>41</v>
+        <v>161</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>209</v>
+        <v>132</v>
       </c>
       <c r="B476" t="n">
-        <v>139</v>
+        <v>183</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="B477" t="n">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="B478" t="n">
-        <v>124</v>
+        <v>235</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>122</v>
+        <v>208</v>
       </c>
       <c r="B479" t="n">
-        <v>211</v>
+        <v>32</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>179</v>
+        <v>86</v>
       </c>
       <c r="B480" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B481" t="n">
-        <v>53</v>
+        <v>161</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="B482" t="n">
-        <v>136</v>
+        <v>229</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="B483" t="n">
-        <v>165</v>
+        <v>151</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>237</v>
+        <v>1</v>
       </c>
       <c r="B484" t="n">
-        <v>216</v>
+        <v>68</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>205</v>
+        <v>92</v>
       </c>
       <c r="B485" t="n">
-        <v>232</v>
+        <v>139</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="B486" t="n">
-        <v>101</v>
+        <v>251</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>199</v>
+        <v>90</v>
       </c>
       <c r="B487" t="n">
-        <v>133</v>
+        <v>248</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B488" t="n">
-        <v>203</v>
+        <v>37</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>26</v>
+        <v>173</v>
       </c>
       <c r="B489" t="n">
-        <v>133</v>
+        <v>112</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>65</v>
+        <v>218</v>
       </c>
       <c r="B490" t="n">
-        <v>72</v>
+        <v>39</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B491" t="n">
-        <v>122</v>
+        <v>30</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>211</v>
+        <v>107</v>
       </c>
       <c r="B492" t="n">
-        <v>193</v>
+        <v>32</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="B493" t="n">
-        <v>198</v>
+        <v>79</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="B494" t="n">
-        <v>59</v>
+        <v>6</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B495" t="n">
-        <v>163</v>
+        <v>185</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>238</v>
+        <v>205</v>
       </c>
       <c r="B496" t="n">
-        <v>207</v>
+        <v>69</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="B497" t="n">
-        <v>194</v>
+        <v>80</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="B498" t="n">
-        <v>211</v>
+        <v>219</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>29</v>
+        <v>136</v>
       </c>
       <c r="B499" t="n">
-        <v>62</v>
+        <v>168</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>15</v>
+        <v>218</v>
       </c>
       <c r="B500" t="n">
-        <v>92</v>
+        <v>65</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="B501" t="n">
-        <v>238</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -4614,10 +4614,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.59091</v>
+        <v>7.62082</v>
       </c>
       <c r="C3" t="n">
-        <v>7.58927</v>
+        <v>7.59171</v>
       </c>
     </row>
     <row r="4">
@@ -4627,10 +4627,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>258.784</v>
+        <v>219.872</v>
       </c>
       <c r="C4" t="n">
-        <v>274.144</v>
+        <v>250.592</v>
       </c>
     </row>
   </sheetData>
@@ -4669,10 +4669,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -4680,10 +4680,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -4691,10 +4691,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -4702,10 +4702,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
         <v>0</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -4713,10 +4713,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -4724,10 +4724,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -4735,10 +4735,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -4746,10 +4746,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -4757,7 +4757,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
         <v>2</v>
@@ -4771,7 +4771,7 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -4779,10 +4779,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -4793,7 +4793,7 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -4801,7 +4801,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
@@ -4812,10 +4812,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -4826,7 +4826,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -4834,10 +4834,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -4845,7 +4845,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -4856,10 +4856,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -4867,7 +4867,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>2</v>
@@ -4878,10 +4878,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -4903,7 +4903,7 @@
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -4911,10 +4911,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -4925,7 +4925,7 @@
         <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -4933,10 +4933,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -4944,7 +4944,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
@@ -4955,10 +4955,10 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -4966,10 +4966,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -4980,7 +4980,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -4991,7 +4991,7 @@
         <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -5002,7 +5002,7 @@
         <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -5010,10 +5010,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -5021,7 +5021,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
         <v>4</v>
@@ -5032,10 +5032,10 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -5046,7 +5046,7 @@
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -5054,7 +5054,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C37" t="n">
         <v>2</v>
@@ -5065,10 +5065,10 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -5076,7 +5076,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C39" t="n">
         <v>3</v>
@@ -5087,10 +5087,10 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -5098,10 +5098,10 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -5112,7 +5112,7 @@
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -5123,7 +5123,7 @@
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -5131,10 +5131,10 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -5145,7 +5145,7 @@
         <v>4</v>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -5156,7 +5156,7 @@
         <v>3</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -5164,10 +5164,10 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -5175,10 +5175,10 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -5186,10 +5186,10 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -5197,10 +5197,10 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -5208,7 +5208,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C51" t="n">
         <v>4</v>
@@ -5222,7 +5222,7 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -5233,7 +5233,7 @@
         <v>2</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -5241,7 +5241,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C54" t="n">
         <v>2</v>
@@ -5252,10 +5252,10 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -5263,10 +5263,10 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
+        <v>2</v>
+      </c>
+      <c r="C56" t="n">
         <v>5</v>
-      </c>
-      <c r="C56" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -5274,10 +5274,10 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -5288,7 +5288,7 @@
         <v>4</v>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -5296,7 +5296,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C59" t="n">
         <v>1</v>
@@ -5307,10 +5307,10 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -5318,10 +5318,10 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -5329,10 +5329,10 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
@@ -5351,10 +5351,10 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -5365,7 +5365,7 @@
         <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -5376,7 +5376,7 @@
         <v>2</v>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -5387,7 +5387,7 @@
         <v>2</v>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -5395,10 +5395,10 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -5406,10 +5406,10 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -5417,10 +5417,10 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -5431,7 +5431,7 @@
         <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -5439,10 +5439,10 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
@@ -5450,7 +5450,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C73" t="n">
         <v>2</v>
@@ -5461,7 +5461,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C74" t="n">
         <v>2</v>
@@ -5472,10 +5472,10 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" t="n">
         <v>0</v>
-      </c>
-      <c r="C75" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -5486,7 +5486,7 @@
         <v>1</v>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -5494,10 +5494,10 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78">
@@ -5508,7 +5508,7 @@
         <v>3</v>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -5516,10 +5516,10 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -5527,7 +5527,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
@@ -5538,10 +5538,10 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -5552,7 +5552,7 @@
         <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
@@ -5560,10 +5560,10 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
@@ -5571,10 +5571,10 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -5585,7 +5585,7 @@
         <v>1</v>
       </c>
       <c r="C85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86">
@@ -5593,10 +5593,10 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -5607,7 +5607,7 @@
         <v>2</v>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
@@ -5615,10 +5615,10 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -5626,10 +5626,10 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
@@ -5637,7 +5637,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C90" t="n">
         <v>1</v>
@@ -5648,10 +5648,10 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C91" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -5659,10 +5659,10 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C92" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
@@ -5670,7 +5670,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C93" t="n">
         <v>1</v>
@@ -5681,10 +5681,10 @@
         <v>92</v>
       </c>
       <c r="B94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C94" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -5692,10 +5692,10 @@
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
@@ -5703,7 +5703,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C96" t="n">
         <v>1</v>
@@ -5714,10 +5714,10 @@
         <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
@@ -5725,10 +5725,10 @@
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -5736,10 +5736,10 @@
         <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -5747,7 +5747,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C100" t="n">
         <v>4</v>
@@ -5761,7 +5761,7 @@
         <v>2</v>
       </c>
       <c r="C101" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
@@ -5769,10 +5769,10 @@
         <v>100</v>
       </c>
       <c r="B102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
@@ -5780,10 +5780,10 @@
         <v>101</v>
       </c>
       <c r="B103" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -5791,10 +5791,10 @@
         <v>102</v>
       </c>
       <c r="B104" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -5802,7 +5802,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C105" t="n">
         <v>2</v>
@@ -5813,10 +5813,10 @@
         <v>104</v>
       </c>
       <c r="B106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -5824,7 +5824,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C107" t="n">
         <v>1</v>
@@ -5835,10 +5835,10 @@
         <v>106</v>
       </c>
       <c r="B108" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C108" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="109">
@@ -5849,7 +5849,7 @@
         <v>2</v>
       </c>
       <c r="C109" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110">
@@ -5860,7 +5860,7 @@
         <v>2</v>
       </c>
       <c r="C110" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="111">
@@ -5868,10 +5868,10 @@
         <v>109</v>
       </c>
       <c r="B111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -5879,10 +5879,10 @@
         <v>110</v>
       </c>
       <c r="B112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C112" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -5890,10 +5890,10 @@
         <v>111</v>
       </c>
       <c r="B113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
@@ -5901,10 +5901,10 @@
         <v>112</v>
       </c>
       <c r="B114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -5912,10 +5912,10 @@
         <v>113</v>
       </c>
       <c r="B115" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
@@ -5923,10 +5923,10 @@
         <v>114</v>
       </c>
       <c r="B116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
@@ -5934,10 +5934,10 @@
         <v>115</v>
       </c>
       <c r="B117" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -5945,7 +5945,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C118" t="n">
         <v>1</v>
@@ -5956,10 +5956,10 @@
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -5967,10 +5967,10 @@
         <v>118</v>
       </c>
       <c r="B120" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -5981,7 +5981,7 @@
         <v>1</v>
       </c>
       <c r="C121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -5989,10 +5989,10 @@
         <v>120</v>
       </c>
       <c r="B122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C122" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="123">
@@ -6000,10 +6000,10 @@
         <v>121</v>
       </c>
       <c r="B123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -6011,10 +6011,10 @@
         <v>122</v>
       </c>
       <c r="B124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
@@ -6022,10 +6022,10 @@
         <v>123</v>
       </c>
       <c r="B125" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126">
@@ -6036,7 +6036,7 @@
         <v>2</v>
       </c>
       <c r="C126" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127">
@@ -6058,7 +6058,7 @@
         <v>4</v>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129">
@@ -6069,7 +6069,7 @@
         <v>2</v>
       </c>
       <c r="C129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -6077,10 +6077,10 @@
         <v>128</v>
       </c>
       <c r="B130" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -6088,7 +6088,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C131" t="n">
         <v>2</v>
@@ -6099,10 +6099,10 @@
         <v>130</v>
       </c>
       <c r="B132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -6113,7 +6113,7 @@
         <v>0</v>
       </c>
       <c r="C133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
@@ -6132,10 +6132,10 @@
         <v>133</v>
       </c>
       <c r="B135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C135" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -6146,7 +6146,7 @@
         <v>2</v>
       </c>
       <c r="C136" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137">
@@ -6154,10 +6154,10 @@
         <v>135</v>
       </c>
       <c r="B137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C137" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138">
@@ -6165,10 +6165,10 @@
         <v>136</v>
       </c>
       <c r="B138" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C138" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -6179,7 +6179,7 @@
         <v>0</v>
       </c>
       <c r="C139" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -6190,7 +6190,7 @@
         <v>0</v>
       </c>
       <c r="C140" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141">
@@ -6198,10 +6198,10 @@
         <v>139</v>
       </c>
       <c r="B141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142">
@@ -6209,10 +6209,10 @@
         <v>140</v>
       </c>
       <c r="B142" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143">
@@ -6220,10 +6220,10 @@
         <v>141</v>
       </c>
       <c r="B143" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
@@ -6231,10 +6231,10 @@
         <v>142</v>
       </c>
       <c r="B144" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C144" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -6245,7 +6245,7 @@
         <v>2</v>
       </c>
       <c r="C145" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -6253,10 +6253,10 @@
         <v>144</v>
       </c>
       <c r="B146" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -6267,7 +6267,7 @@
         <v>2</v>
       </c>
       <c r="C147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -6275,7 +6275,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C148" t="n">
         <v>1</v>
@@ -6289,7 +6289,7 @@
         <v>3</v>
       </c>
       <c r="C149" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150">
@@ -6297,7 +6297,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C150" t="n">
         <v>1</v>
@@ -6308,10 +6308,10 @@
         <v>149</v>
       </c>
       <c r="B151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C151" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="152">
@@ -6319,10 +6319,10 @@
         <v>150</v>
       </c>
       <c r="B152" t="n">
+        <v>2</v>
+      </c>
+      <c r="C152" t="n">
         <v>0</v>
-      </c>
-      <c r="C152" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="153">
@@ -6330,10 +6330,10 @@
         <v>151</v>
       </c>
       <c r="B153" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C153" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="154">
@@ -6341,10 +6341,10 @@
         <v>152</v>
       </c>
       <c r="B154" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155">
@@ -6363,10 +6363,10 @@
         <v>154</v>
       </c>
       <c r="B156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
@@ -6374,7 +6374,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C157" t="n">
         <v>2</v>
@@ -6385,10 +6385,10 @@
         <v>156</v>
       </c>
       <c r="B158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
@@ -6399,7 +6399,7 @@
         <v>1</v>
       </c>
       <c r="C159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
@@ -6410,7 +6410,7 @@
         <v>2</v>
       </c>
       <c r="C160" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -6418,10 +6418,10 @@
         <v>159</v>
       </c>
       <c r="B161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
@@ -6429,7 +6429,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C162" t="n">
         <v>1</v>
@@ -6443,7 +6443,7 @@
         <v>1</v>
       </c>
       <c r="C163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
@@ -6451,10 +6451,10 @@
         <v>162</v>
       </c>
       <c r="B164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C164" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="165">
@@ -6462,10 +6462,10 @@
         <v>163</v>
       </c>
       <c r="B165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C165" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="166">
@@ -6476,7 +6476,7 @@
         <v>1</v>
       </c>
       <c r="C166" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="167">
@@ -6484,10 +6484,10 @@
         <v>165</v>
       </c>
       <c r="B167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C167" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -6495,7 +6495,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C168" t="n">
         <v>2</v>
@@ -6506,10 +6506,10 @@
         <v>167</v>
       </c>
       <c r="B169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C169" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170">
@@ -6517,10 +6517,10 @@
         <v>168</v>
       </c>
       <c r="B170" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C170" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="171">
@@ -6528,7 +6528,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C171" t="n">
         <v>1</v>
@@ -6539,7 +6539,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C172" t="n">
         <v>2</v>
@@ -6561,10 +6561,10 @@
         <v>172</v>
       </c>
       <c r="B174" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -6575,7 +6575,7 @@
         <v>2</v>
       </c>
       <c r="C175" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
@@ -6583,10 +6583,10 @@
         <v>174</v>
       </c>
       <c r="B176" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C176" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
@@ -6605,10 +6605,10 @@
         <v>176</v>
       </c>
       <c r="B178" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C178" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
@@ -6616,10 +6616,10 @@
         <v>177</v>
       </c>
       <c r="B179" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
@@ -6627,10 +6627,10 @@
         <v>178</v>
       </c>
       <c r="B180" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181">
@@ -6649,10 +6649,10 @@
         <v>180</v>
       </c>
       <c r="B182" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C182" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -6663,7 +6663,7 @@
         <v>2</v>
       </c>
       <c r="C183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -6671,10 +6671,10 @@
         <v>182</v>
       </c>
       <c r="B184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185">
@@ -6682,10 +6682,10 @@
         <v>183</v>
       </c>
       <c r="B185" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -6693,10 +6693,10 @@
         <v>184</v>
       </c>
       <c r="B186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C186" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187">
@@ -6707,7 +6707,7 @@
         <v>3</v>
       </c>
       <c r="C187" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="188">
@@ -6715,7 +6715,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C188" t="n">
         <v>1</v>
@@ -6729,7 +6729,7 @@
         <v>1</v>
       </c>
       <c r="C189" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="190">
@@ -6737,10 +6737,10 @@
         <v>188</v>
       </c>
       <c r="B190" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="191">
@@ -6748,10 +6748,10 @@
         <v>189</v>
       </c>
       <c r="B191" t="n">
+        <v>3</v>
+      </c>
+      <c r="C191" t="n">
         <v>4</v>
-      </c>
-      <c r="C191" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -6759,7 +6759,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C192" t="n">
         <v>2</v>
@@ -6773,7 +6773,7 @@
         <v>3</v>
       </c>
       <c r="C193" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194">
@@ -6781,10 +6781,10 @@
         <v>192</v>
       </c>
       <c r="B194" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C194" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195">
@@ -6792,10 +6792,10 @@
         <v>193</v>
       </c>
       <c r="B195" t="n">
+        <v>4</v>
+      </c>
+      <c r="C195" t="n">
         <v>5</v>
-      </c>
-      <c r="C195" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="196">
@@ -6803,10 +6803,10 @@
         <v>194</v>
       </c>
       <c r="B196" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C196" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -6814,10 +6814,10 @@
         <v>195</v>
       </c>
       <c r="B197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C197" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
@@ -6825,10 +6825,10 @@
         <v>196</v>
       </c>
       <c r="B198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -6836,10 +6836,10 @@
         <v>197</v>
       </c>
       <c r="B199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C199" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200">
@@ -6847,10 +6847,10 @@
         <v>198</v>
       </c>
       <c r="B200" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C200" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201">
@@ -6858,10 +6858,10 @@
         <v>199</v>
       </c>
       <c r="B201" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202">
@@ -6869,10 +6869,10 @@
         <v>200</v>
       </c>
       <c r="B202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C202" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203">
@@ -6883,7 +6883,7 @@
         <v>3</v>
       </c>
       <c r="C203" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204">
@@ -6891,10 +6891,10 @@
         <v>202</v>
       </c>
       <c r="B204" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C204" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="205">
@@ -6902,10 +6902,10 @@
         <v>203</v>
       </c>
       <c r="B205" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -6913,10 +6913,10 @@
         <v>204</v>
       </c>
       <c r="B206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C206" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="207">
@@ -6927,7 +6927,7 @@
         <v>4</v>
       </c>
       <c r="C207" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -6938,7 +6938,7 @@
         <v>3</v>
       </c>
       <c r="C208" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209">
@@ -6946,10 +6946,10 @@
         <v>207</v>
       </c>
       <c r="B209" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C209" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="210">
@@ -6957,10 +6957,10 @@
         <v>208</v>
       </c>
       <c r="B210" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C210" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211">
@@ -6968,10 +6968,10 @@
         <v>209</v>
       </c>
       <c r="B211" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C211" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="212">
@@ -6979,7 +6979,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C212" t="n">
         <v>4</v>
@@ -6993,7 +6993,7 @@
         <v>2</v>
       </c>
       <c r="C213" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214">
@@ -7001,10 +7001,10 @@
         <v>212</v>
       </c>
       <c r="B214" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C214" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="215">
@@ -7026,7 +7026,7 @@
         <v>2</v>
       </c>
       <c r="C216" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="217">
@@ -7034,10 +7034,10 @@
         <v>215</v>
       </c>
       <c r="B217" t="n">
+        <v>1</v>
+      </c>
+      <c r="C217" t="n">
         <v>0</v>
-      </c>
-      <c r="C217" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="218">
@@ -7045,10 +7045,10 @@
         <v>216</v>
       </c>
       <c r="B218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C218" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219">
@@ -7056,10 +7056,10 @@
         <v>217</v>
       </c>
       <c r="B219" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="220">
@@ -7067,10 +7067,10 @@
         <v>218</v>
       </c>
       <c r="B220" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
@@ -7078,10 +7078,10 @@
         <v>219</v>
       </c>
       <c r="B221" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C221" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="222">
@@ -7092,7 +7092,7 @@
         <v>1</v>
       </c>
       <c r="C222" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
@@ -7100,10 +7100,10 @@
         <v>221</v>
       </c>
       <c r="B223" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C223" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="224">
@@ -7111,10 +7111,10 @@
         <v>222</v>
       </c>
       <c r="B224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C224" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225">
@@ -7122,10 +7122,10 @@
         <v>223</v>
       </c>
       <c r="B225" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C225" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226">
@@ -7136,7 +7136,7 @@
         <v>1</v>
       </c>
       <c r="C226" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227">
@@ -7144,10 +7144,10 @@
         <v>225</v>
       </c>
       <c r="B227" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C227" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228">
@@ -7155,10 +7155,10 @@
         <v>226</v>
       </c>
       <c r="B228" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C228" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229">
@@ -7166,10 +7166,10 @@
         <v>227</v>
       </c>
       <c r="B229" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C229" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230">
@@ -7177,10 +7177,10 @@
         <v>228</v>
       </c>
       <c r="B230" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
@@ -7188,10 +7188,10 @@
         <v>229</v>
       </c>
       <c r="B231" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C231" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="232">
@@ -7210,10 +7210,10 @@
         <v>231</v>
       </c>
       <c r="B233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C233" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="234">
@@ -7232,10 +7232,10 @@
         <v>233</v>
       </c>
       <c r="B235" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C235" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
@@ -7243,10 +7243,10 @@
         <v>234</v>
       </c>
       <c r="B236" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C236" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237">
@@ -7254,10 +7254,10 @@
         <v>235</v>
       </c>
       <c r="B237" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C237" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238">
@@ -7265,10 +7265,10 @@
         <v>236</v>
       </c>
       <c r="B238" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C238" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="239">
@@ -7276,7 +7276,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C239" t="n">
         <v>2</v>
@@ -7287,10 +7287,10 @@
         <v>238</v>
       </c>
       <c r="B240" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C240" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241">
@@ -7298,10 +7298,10 @@
         <v>239</v>
       </c>
       <c r="B241" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C241" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="242">
@@ -7309,7 +7309,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C242" t="n">
         <v>1</v>
@@ -7320,10 +7320,10 @@
         <v>241</v>
       </c>
       <c r="B243" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C243" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
@@ -7331,10 +7331,10 @@
         <v>242</v>
       </c>
       <c r="B244" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C244" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245">
@@ -7342,7 +7342,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C245" t="n">
         <v>1</v>
@@ -7356,7 +7356,7 @@
         <v>2</v>
       </c>
       <c r="C246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247">
@@ -7367,7 +7367,7 @@
         <v>1</v>
       </c>
       <c r="C247" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248">
@@ -7375,10 +7375,10 @@
         <v>246</v>
       </c>
       <c r="B248" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C248" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -7386,7 +7386,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C249" t="n">
         <v>2</v>
@@ -7397,10 +7397,10 @@
         <v>248</v>
       </c>
       <c r="B250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C250" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -7408,10 +7408,10 @@
         <v>249</v>
       </c>
       <c r="B251" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C251" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="252">
@@ -7419,7 +7419,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C252" t="n">
         <v>2</v>
@@ -7430,10 +7430,10 @@
         <v>251</v>
       </c>
       <c r="B253" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C253" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="254">
@@ -7444,7 +7444,7 @@
         <v>1</v>
       </c>
       <c r="C254" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
@@ -7463,7 +7463,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C256" t="n">
         <v>3</v>
@@ -7474,10 +7474,10 @@
         <v>255</v>
       </c>
       <c r="B257" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C257" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/backend/RNG_Report.xlsx
+++ b/backend/RNG_Report.xlsx
@@ -565,263 +565,263 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68</v>
+        <v>127</v>
       </c>
       <c r="B2" t="n">
-        <v>151</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>230</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>82</v>
+        <v>244</v>
       </c>
       <c r="B4" t="n">
-        <v>235</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>45</v>
+        <v>192</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>249</v>
+        <v>96</v>
       </c>
       <c r="B7" t="n">
-        <v>213</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>202</v>
+        <v>137</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>44</v>
+        <v>143</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="B10" t="n">
-        <v>238</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="B11" t="n">
-        <v>239</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="B12" t="n">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>18</v>
+        <v>223</v>
       </c>
       <c r="B13" t="n">
-        <v>231</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>98</v>
+        <v>171</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>95</v>
+        <v>24</v>
       </c>
       <c r="B15" t="n">
-        <v>61</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>181</v>
+        <v>129</v>
       </c>
       <c r="B16" t="n">
-        <v>123</v>
+        <v>215</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>235</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="B18" t="n">
-        <v>239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>208</v>
+        <v>24</v>
       </c>
       <c r="B20" t="n">
-        <v>60</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>210</v>
+        <v>72</v>
       </c>
       <c r="B21" t="n">
-        <v>62</v>
+        <v>229</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>206</v>
+        <v>253</v>
       </c>
       <c r="B22" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="B23" t="n">
-        <v>229</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>152</v>
+        <v>193</v>
       </c>
       <c r="B24" t="n">
-        <v>6</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B25" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>194</v>
+        <v>137</v>
       </c>
       <c r="B26" t="n">
-        <v>87</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>190</v>
+        <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>21</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>11</v>
+        <v>149</v>
       </c>
       <c r="B28" t="n">
-        <v>244</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B29" t="n">
-        <v>46</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B30" t="n">
-        <v>251</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>148</v>
+        <v>48</v>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="B32" t="n">
-        <v>247</v>
+        <v>186</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>232</v>
+        <v>176</v>
       </c>
       <c r="B33" t="n">
-        <v>83</v>
+        <v>165</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>191</v>
+        <v>71</v>
       </c>
       <c r="B34" t="n">
         <v>54</v>
@@ -829,591 +829,591 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="B35" t="n">
-        <v>140</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="B36" t="n">
-        <v>24</v>
+        <v>190</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>64</v>
+        <v>160</v>
       </c>
       <c r="B37" t="n">
-        <v>72</v>
+        <v>193</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>180</v>
+        <v>249</v>
       </c>
       <c r="B38" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>31</v>
+        <v>100</v>
       </c>
       <c r="B39" t="n">
-        <v>212</v>
+        <v>163</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B40" t="n">
-        <v>230</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B41" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>193</v>
+        <v>74</v>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>112</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>6</v>
+        <v>104</v>
       </c>
       <c r="B44" t="n">
-        <v>178</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="B45" t="n">
-        <v>232</v>
+        <v>123</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>89</v>
+        <v>176</v>
       </c>
       <c r="B46" t="n">
-        <v>63</v>
+        <v>237</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>250</v>
+        <v>121</v>
       </c>
       <c r="B47" t="n">
-        <v>143</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>158</v>
+        <v>123</v>
       </c>
       <c r="B48" t="n">
-        <v>249</v>
+        <v>173</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>88</v>
+        <v>138</v>
       </c>
       <c r="B49" t="n">
-        <v>72</v>
+        <v>208</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B50" t="n">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>238</v>
+        <v>34</v>
       </c>
       <c r="B51" t="n">
-        <v>6</v>
+        <v>173</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="B52" t="n">
-        <v>54</v>
+        <v>177</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="B53" t="n">
-        <v>32</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="B54" t="n">
-        <v>253</v>
+        <v>224</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>156</v>
+        <v>251</v>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>162</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="B56" t="n">
-        <v>194</v>
+        <v>235</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>32</v>
+        <v>195</v>
       </c>
       <c r="B57" t="n">
-        <v>225</v>
+        <v>203</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="B58" t="n">
-        <v>177</v>
+        <v>24</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>203</v>
+        <v>245</v>
       </c>
       <c r="B59" t="n">
-        <v>191</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>66</v>
+        <v>122</v>
       </c>
       <c r="B60" t="n">
-        <v>162</v>
+        <v>240</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>178</v>
+        <v>215</v>
       </c>
       <c r="B62" t="n">
-        <v>175</v>
+        <v>148</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>106</v>
+        <v>149</v>
       </c>
       <c r="B63" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>194</v>
+        <v>4</v>
       </c>
       <c r="B64" t="n">
-        <v>178</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="B65" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="B66" t="n">
-        <v>210</v>
+        <v>228</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>225</v>
+        <v>26</v>
       </c>
       <c r="B67" t="n">
-        <v>239</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>228</v>
+        <v>171</v>
       </c>
       <c r="B68" t="n">
-        <v>168</v>
+        <v>201</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>241</v>
+        <v>142</v>
       </c>
       <c r="B69" t="n">
-        <v>253</v>
+        <v>246</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="B70" t="n">
-        <v>128</v>
+        <v>245</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="B71" t="n">
-        <v>166</v>
+        <v>191</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>191</v>
+        <v>58</v>
       </c>
       <c r="B72" t="n">
-        <v>105</v>
+        <v>181</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>160</v>
+        <v>244</v>
       </c>
       <c r="B73" t="n">
-        <v>212</v>
+        <v>154</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>202</v>
+        <v>51</v>
       </c>
       <c r="B74" t="n">
-        <v>76</v>
+        <v>166</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="B75" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B76" t="n">
-        <v>103</v>
+        <v>154</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B77" t="n">
-        <v>20</v>
+        <v>112</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>58</v>
+        <v>239</v>
       </c>
       <c r="B78" t="n">
-        <v>81</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>205</v>
+        <v>126</v>
       </c>
       <c r="B79" t="n">
-        <v>95</v>
+        <v>245</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>27</v>
+        <v>229</v>
       </c>
       <c r="B80" t="n">
-        <v>236</v>
+        <v>190</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>173</v>
+        <v>253</v>
       </c>
       <c r="B81" t="n">
-        <v>181</v>
+        <v>172</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>159</v>
+        <v>251</v>
       </c>
       <c r="B82" t="n">
-        <v>180</v>
+        <v>156</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="B83" t="n">
-        <v>8</v>
+        <v>196</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>71</v>
+        <v>150</v>
       </c>
       <c r="B84" t="n">
-        <v>189</v>
+        <v>44</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="B85" t="n">
-        <v>89</v>
+        <v>211</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>6</v>
+        <v>167</v>
       </c>
       <c r="B86" t="n">
-        <v>138</v>
+        <v>129</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="B87" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>70</v>
+        <v>125</v>
       </c>
       <c r="B88" t="n">
-        <v>44</v>
+        <v>149</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>101</v>
+        <v>171</v>
       </c>
       <c r="B89" t="n">
-        <v>29</v>
+        <v>110</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>31</v>
+        <v>247</v>
       </c>
       <c r="B90" t="n">
-        <v>58</v>
+        <v>207</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>11</v>
+        <v>221</v>
       </c>
       <c r="B91" t="n">
-        <v>81</v>
+        <v>154</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="B92" t="n">
-        <v>99</v>
+        <v>250</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>240</v>
+        <v>19</v>
       </c>
       <c r="B93" t="n">
-        <v>193</v>
+        <v>217</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="B94" t="n">
-        <v>209</v>
+        <v>99</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="B95" t="n">
-        <v>60</v>
+        <v>238</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>2</v>
+        <v>183</v>
       </c>
       <c r="B96" t="n">
-        <v>197</v>
+        <v>166</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>74</v>
+        <v>191</v>
       </c>
       <c r="B97" t="n">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>214</v>
+        <v>139</v>
       </c>
       <c r="B98" t="n">
-        <v>252</v>
+        <v>217</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>193</v>
+        <v>166</v>
       </c>
       <c r="B99" t="n">
-        <v>189</v>
+        <v>53</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B100" t="n">
-        <v>9</v>
+        <v>230</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="B101" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>193</v>
+        <v>254</v>
       </c>
       <c r="B102" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="B103" t="n">
-        <v>176</v>
+        <v>200</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>166</v>
+        <v>17</v>
       </c>
       <c r="B104" t="n">
-        <v>107</v>
+        <v>59</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>113</v>
+        <v>29</v>
       </c>
       <c r="B105" t="n">
-        <v>58</v>
+        <v>198</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>141</v>
+        <v>47</v>
       </c>
       <c r="B106" t="n">
-        <v>152</v>
+        <v>131</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="B107" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>47</v>
+        <v>191</v>
       </c>
       <c r="B108" t="n">
         <v>181</v>
@@ -1421,3146 +1421,3146 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>45</v>
+        <v>78</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>2</v>
+        <v>145</v>
       </c>
       <c r="B110" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>56</v>
+        <v>119</v>
       </c>
       <c r="B111" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="B112" t="n">
-        <v>1</v>
+        <v>211</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>99</v>
+        <v>172</v>
       </c>
       <c r="B113" t="n">
-        <v>162</v>
+        <v>51</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>198</v>
+        <v>248</v>
       </c>
       <c r="B114" t="n">
-        <v>167</v>
+        <v>201</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="B115" t="n">
-        <v>67</v>
+        <v>182</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>197</v>
+        <v>55</v>
       </c>
       <c r="B116" t="n">
-        <v>249</v>
+        <v>164</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="B117" t="n">
-        <v>188</v>
+        <v>23</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>143</v>
+        <v>2</v>
       </c>
       <c r="B118" t="n">
-        <v>83</v>
+        <v>119</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="B119" t="n">
-        <v>10</v>
+        <v>218</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="B120" t="n">
-        <v>226</v>
+        <v>29</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>179</v>
+        <v>116</v>
       </c>
       <c r="B121" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="B122" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="B123" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="B124" t="n">
-        <v>4</v>
+        <v>168</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>237</v>
+        <v>130</v>
       </c>
       <c r="B125" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>205</v>
+        <v>56</v>
       </c>
       <c r="B126" t="n">
-        <v>168</v>
+        <v>183</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>147</v>
+        <v>211</v>
       </c>
       <c r="B127" t="n">
-        <v>201</v>
+        <v>170</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="B128" t="n">
-        <v>103</v>
+        <v>128</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>177</v>
+        <v>47</v>
       </c>
       <c r="B129" t="n">
-        <v>162</v>
+        <v>129</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>26</v>
+        <v>193</v>
       </c>
       <c r="B130" t="n">
-        <v>57</v>
+        <v>88</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B131" t="n">
-        <v>158</v>
+        <v>91</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126</v>
+        <v>176</v>
       </c>
       <c r="B132" t="n">
-        <v>207</v>
+        <v>24</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>211</v>
+        <v>86</v>
       </c>
       <c r="B133" t="n">
-        <v>222</v>
+        <v>149</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>123</v>
+        <v>225</v>
       </c>
       <c r="B134" t="n">
-        <v>162</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>132</v>
+        <v>206</v>
       </c>
       <c r="B135" t="n">
-        <v>169</v>
+        <v>133</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B136" t="n">
-        <v>147</v>
+        <v>21</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>238</v>
+        <v>103</v>
       </c>
       <c r="B137" t="n">
-        <v>163</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>170</v>
+        <v>89</v>
       </c>
       <c r="B138" t="n">
-        <v>200</v>
+        <v>174</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="B139" t="n">
-        <v>66</v>
+        <v>242</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>29</v>
+        <v>109</v>
       </c>
       <c r="B140" t="n">
-        <v>236</v>
+        <v>185</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>15</v>
+        <v>210</v>
       </c>
       <c r="B141" t="n">
-        <v>31</v>
+        <v>240</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="B142" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>134</v>
+        <v>243</v>
       </c>
       <c r="B143" t="n">
-        <v>7</v>
+        <v>192</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>209</v>
+        <v>80</v>
       </c>
       <c r="B144" t="n">
-        <v>236</v>
+        <v>211</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>230</v>
+        <v>15</v>
       </c>
       <c r="B145" t="n">
-        <v>52</v>
+        <v>251</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B146" t="n">
-        <v>49</v>
+        <v>164</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="B147" t="n">
-        <v>141</v>
+        <v>124</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="B148" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>11</v>
+        <v>169</v>
       </c>
       <c r="B149" t="n">
-        <v>208</v>
+        <v>184</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="B150" t="n">
-        <v>219</v>
+        <v>188</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="B151" t="n">
-        <v>129</v>
+        <v>241</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>90</v>
+        <v>240</v>
       </c>
       <c r="B152" t="n">
-        <v>74</v>
+        <v>180</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>98</v>
+        <v>251</v>
       </c>
       <c r="B153" t="n">
-        <v>151</v>
+        <v>233</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B154" t="n">
-        <v>106</v>
+        <v>33</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>28</v>
+        <v>148</v>
       </c>
       <c r="B155" t="n">
-        <v>71</v>
+        <v>139</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="B156" t="n">
-        <v>44</v>
+        <v>237</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>56</v>
+        <v>189</v>
       </c>
       <c r="B157" t="n">
-        <v>221</v>
+        <v>156</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B158" t="n">
-        <v>170</v>
+        <v>108</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="B159" t="n">
-        <v>22</v>
+        <v>220</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>163</v>
+        <v>111</v>
       </c>
       <c r="B160" t="n">
-        <v>80</v>
+        <v>153</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>177</v>
+        <v>110</v>
       </c>
       <c r="B161" t="n">
-        <v>241</v>
+        <v>25</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B162" t="n">
-        <v>187</v>
+        <v>117</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>156</v>
+        <v>217</v>
       </c>
       <c r="B163" t="n">
-        <v>8</v>
+        <v>52</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B164" t="n">
-        <v>6</v>
+        <v>186</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="B165" t="n">
-        <v>202</v>
+        <v>211</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>93</v>
+        <v>197</v>
       </c>
       <c r="B166" t="n">
-        <v>107</v>
+        <v>50</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>223</v>
+        <v>97</v>
       </c>
       <c r="B167" t="n">
-        <v>49</v>
+        <v>76</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>147</v>
+        <v>222</v>
       </c>
       <c r="B168" t="n">
-        <v>248</v>
+        <v>10</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>38</v>
+        <v>217</v>
       </c>
       <c r="B169" t="n">
-        <v>55</v>
+        <v>112</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="B170" t="n">
-        <v>253</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>16</v>
+        <v>198</v>
       </c>
       <c r="B171" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="B172" t="n">
-        <v>35</v>
+        <v>106</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>226</v>
+        <v>195</v>
       </c>
       <c r="B173" t="n">
-        <v>114</v>
+        <v>139</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128</v>
+        <v>236</v>
       </c>
       <c r="B174" t="n">
-        <v>106</v>
+        <v>226</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="B175" t="n">
-        <v>231</v>
+        <v>188</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>236</v>
+        <v>19</v>
       </c>
       <c r="B176" t="n">
-        <v>234</v>
+        <v>12</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="B177" t="n">
-        <v>60</v>
+        <v>23</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="B178" t="n">
-        <v>185</v>
+        <v>118</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="B179" t="n">
-        <v>207</v>
+        <v>36</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="B180" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>95</v>
+        <v>215</v>
       </c>
       <c r="B181" t="n">
-        <v>83</v>
+        <v>156</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>195</v>
+        <v>100</v>
       </c>
       <c r="B182" t="n">
-        <v>251</v>
+        <v>170</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>224</v>
+        <v>54</v>
       </c>
       <c r="B183" t="n">
-        <v>214</v>
+        <v>42</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="B184" t="n">
-        <v>168</v>
+        <v>147</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B185" t="n">
-        <v>13</v>
+        <v>176</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>171</v>
+        <v>47</v>
       </c>
       <c r="B186" t="n">
-        <v>118</v>
+        <v>50</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>167</v>
+        <v>44</v>
       </c>
       <c r="B187" t="n">
-        <v>177</v>
+        <v>191</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="B188" t="n">
-        <v>81</v>
+        <v>127</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="B189" t="n">
-        <v>86</v>
+        <v>225</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>198</v>
+        <v>14</v>
       </c>
       <c r="B190" t="n">
-        <v>233</v>
+        <v>244</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>169</v>
+        <v>38</v>
       </c>
       <c r="B191" t="n">
-        <v>206</v>
+        <v>7</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>174</v>
+        <v>110</v>
       </c>
       <c r="B192" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>243</v>
+        <v>214</v>
       </c>
       <c r="B193" t="n">
-        <v>59</v>
+        <v>244</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>79</v>
+        <v>165</v>
       </c>
       <c r="B194" t="n">
-        <v>90</v>
+        <v>222</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>186</v>
+        <v>254</v>
       </c>
       <c r="B195" t="n">
-        <v>63</v>
+        <v>85</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B196" t="n">
-        <v>254</v>
+        <v>72</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>143</v>
+        <v>192</v>
       </c>
       <c r="B197" t="n">
-        <v>214</v>
+        <v>142</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="B198" t="n">
-        <v>168</v>
+        <v>237</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>187</v>
+        <v>222</v>
       </c>
       <c r="B199" t="n">
-        <v>111</v>
+        <v>126</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>254</v>
+        <v>194</v>
       </c>
       <c r="B200" t="n">
-        <v>151</v>
+        <v>229</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B201" t="n">
-        <v>139</v>
+        <v>58</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="B202" t="n">
-        <v>160</v>
+        <v>69</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>61</v>
+        <v>166</v>
       </c>
       <c r="B203" t="n">
-        <v>224</v>
+        <v>47</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>85</v>
+        <v>193</v>
       </c>
       <c r="B204" t="n">
-        <v>40</v>
+        <v>153</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="B205" t="n">
-        <v>140</v>
+        <v>56</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>10</v>
+        <v>118</v>
       </c>
       <c r="B206" t="n">
-        <v>185</v>
+        <v>199</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>48</v>
+        <v>238</v>
       </c>
       <c r="B207" t="n">
-        <v>24</v>
+        <v>57</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B208" t="n">
-        <v>123</v>
+        <v>30</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B209" t="n">
-        <v>62</v>
+        <v>254</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>112</v>
+        <v>180</v>
       </c>
       <c r="B210" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="B211" t="n">
-        <v>90</v>
+        <v>168</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>2</v>
+        <v>81</v>
       </c>
       <c r="B212" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="B213" t="n">
-        <v>204</v>
+        <v>56</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="B214" t="n">
-        <v>39</v>
+        <v>214</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B215" t="n">
-        <v>162</v>
+        <v>21</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="B216" t="n">
-        <v>231</v>
+        <v>37</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="B217" t="n">
-        <v>159</v>
+        <v>166</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>81</v>
+        <v>221</v>
       </c>
       <c r="B218" t="n">
-        <v>12</v>
+        <v>114</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>157</v>
+        <v>66</v>
       </c>
       <c r="B219" t="n">
-        <v>19</v>
+        <v>189</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="B220" t="n">
-        <v>50</v>
+        <v>248</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="B221" t="n">
-        <v>155</v>
+        <v>2</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>235</v>
+        <v>33</v>
       </c>
       <c r="B222" t="n">
-        <v>168</v>
+        <v>117</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>242</v>
+        <v>198</v>
       </c>
       <c r="B223" t="n">
-        <v>100</v>
+        <v>48</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>117</v>
+        <v>175</v>
       </c>
       <c r="B224" t="n">
-        <v>228</v>
+        <v>103</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="B225" t="n">
-        <v>210</v>
+        <v>135</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="B226" t="n">
-        <v>187</v>
+        <v>128</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>47</v>
+        <v>157</v>
       </c>
       <c r="B227" t="n">
-        <v>224</v>
+        <v>243</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>33</v>
+        <v>230</v>
       </c>
       <c r="B228" t="n">
-        <v>226</v>
+        <v>27</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>144</v>
+        <v>224</v>
       </c>
       <c r="B229" t="n">
-        <v>153</v>
+        <v>213</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>252</v>
+        <v>127</v>
       </c>
       <c r="B230" t="n">
-        <v>164</v>
+        <v>225</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>142</v>
+        <v>54</v>
       </c>
       <c r="B231" t="n">
-        <v>249</v>
+        <v>155</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>189</v>
+        <v>24</v>
       </c>
       <c r="B232" t="n">
-        <v>11</v>
+        <v>57</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="B233" t="n">
-        <v>94</v>
+        <v>112</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>234</v>
+        <v>118</v>
       </c>
       <c r="B234" t="n">
-        <v>91</v>
+        <v>38</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>124</v>
+        <v>50</v>
       </c>
       <c r="B235" t="n">
-        <v>225</v>
+        <v>174</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>170</v>
+        <v>221</v>
       </c>
       <c r="B236" t="n">
-        <v>202</v>
+        <v>57</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>63</v>
+        <v>254</v>
       </c>
       <c r="B237" t="n">
-        <v>52</v>
+        <v>199</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="B238" t="n">
-        <v>85</v>
+        <v>182</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>88</v>
+        <v>138</v>
       </c>
       <c r="B239" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B240" t="n">
-        <v>193</v>
+        <v>28</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="B241" t="n">
-        <v>85</v>
+        <v>150</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>155</v>
+        <v>107</v>
       </c>
       <c r="B242" t="n">
-        <v>135</v>
+        <v>210</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>197</v>
+        <v>93</v>
       </c>
       <c r="B243" t="n">
-        <v>187</v>
+        <v>18</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>213</v>
+        <v>148</v>
       </c>
       <c r="B244" t="n">
-        <v>179</v>
+        <v>47</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>126</v>
+        <v>43</v>
       </c>
       <c r="B245" t="n">
-        <v>129</v>
+        <v>165</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="B246" t="n">
-        <v>201</v>
+        <v>222</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>244</v>
+        <v>28</v>
       </c>
       <c r="B247" t="n">
-        <v>182</v>
+        <v>59</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>250</v>
+        <v>32</v>
       </c>
       <c r="B248" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="B249" t="n">
-        <v>93</v>
+        <v>139</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="B250" t="n">
-        <v>81</v>
+        <v>138</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="B251" t="n">
-        <v>236</v>
+        <v>217</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B252" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="B253" t="n">
-        <v>156</v>
+        <v>53</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B254" t="n">
-        <v>198</v>
+        <v>210</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="B255" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="B256" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>219</v>
+        <v>32</v>
       </c>
       <c r="B257" t="n">
-        <v>120</v>
+        <v>207</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B258" t="n">
-        <v>98</v>
+        <v>178</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="B259" t="n">
-        <v>174</v>
+        <v>67</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>236</v>
+        <v>32</v>
       </c>
       <c r="B260" t="n">
-        <v>82</v>
+        <v>170</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>123</v>
+        <v>46</v>
       </c>
       <c r="B261" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>237</v>
+        <v>39</v>
       </c>
       <c r="B262" t="n">
-        <v>249</v>
+        <v>147</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>113</v>
+        <v>203</v>
       </c>
       <c r="B263" t="n">
-        <v>183</v>
+        <v>118</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>144</v>
+        <v>232</v>
       </c>
       <c r="B264" t="n">
-        <v>108</v>
+        <v>169</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="B265" t="n">
-        <v>232</v>
+        <v>142</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>209</v>
+        <v>33</v>
       </c>
       <c r="B266" t="n">
-        <v>204</v>
+        <v>19</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="B267" t="n">
-        <v>66</v>
+        <v>214</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>27</v>
+        <v>142</v>
       </c>
       <c r="B268" t="n">
-        <v>98</v>
+        <v>110</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>203</v>
+        <v>85</v>
       </c>
       <c r="B269" t="n">
-        <v>134</v>
+        <v>235</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>87</v>
+        <v>208</v>
       </c>
       <c r="B270" t="n">
-        <v>154</v>
+        <v>191</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="B271" t="n">
-        <v>149</v>
+        <v>121</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="B272" t="n">
-        <v>13</v>
+        <v>151</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="B273" t="n">
-        <v>184</v>
+        <v>116</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>189</v>
+        <v>242</v>
       </c>
       <c r="B274" t="n">
-        <v>88</v>
+        <v>57</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>141</v>
+        <v>99</v>
       </c>
       <c r="B275" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="B276" t="n">
-        <v>98</v>
+        <v>189</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>168</v>
+        <v>48</v>
       </c>
       <c r="B277" t="n">
-        <v>30</v>
+        <v>199</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>212</v>
+        <v>146</v>
       </c>
       <c r="B278" t="n">
-        <v>189</v>
+        <v>229</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="B279" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B280" t="n">
-        <v>116</v>
+        <v>131</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="B281" t="n">
-        <v>68</v>
+        <v>86</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="B282" t="n">
-        <v>108</v>
+        <v>191</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="B283" t="n">
-        <v>245</v>
+        <v>254</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>155</v>
+        <v>100</v>
       </c>
       <c r="B284" t="n">
-        <v>79</v>
+        <v>1</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="B285" t="n">
-        <v>216</v>
+        <v>157</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="B286" t="n">
-        <v>200</v>
+        <v>167</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="B287" t="n">
-        <v>122</v>
+        <v>47</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="B288" t="n">
-        <v>61</v>
+        <v>42</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>243</v>
+        <v>129</v>
       </c>
       <c r="B289" t="n">
-        <v>126</v>
+        <v>78</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>192</v>
+        <v>39</v>
       </c>
       <c r="B290" t="n">
-        <v>54</v>
+        <v>226</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="B291" t="n">
-        <v>45</v>
+        <v>126</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>182</v>
+        <v>27</v>
       </c>
       <c r="B292" t="n">
-        <v>237</v>
+        <v>143</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>13</v>
+        <v>133</v>
       </c>
       <c r="B293" t="n">
-        <v>131</v>
+        <v>186</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="B294" t="n">
-        <v>157</v>
+        <v>236</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>112</v>
+        <v>16</v>
       </c>
       <c r="B295" t="n">
-        <v>106</v>
+        <v>69</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="B296" t="n">
-        <v>30</v>
+        <v>106</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>204</v>
+        <v>246</v>
       </c>
       <c r="B297" t="n">
-        <v>207</v>
+        <v>137</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>41</v>
+        <v>242</v>
       </c>
       <c r="B298" t="n">
-        <v>21</v>
+        <v>134</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="B299" t="n">
-        <v>127</v>
+        <v>12</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>151</v>
+        <v>96</v>
       </c>
       <c r="B300" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>148</v>
+        <v>232</v>
       </c>
       <c r="B301" t="n">
-        <v>66</v>
+        <v>199</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B302" t="n">
-        <v>231</v>
+        <v>46</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>30</v>
+        <v>205</v>
       </c>
       <c r="B303" t="n">
-        <v>152</v>
+        <v>71</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>247</v>
+        <v>189</v>
       </c>
       <c r="B304" t="n">
-        <v>83</v>
+        <v>67</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>174</v>
+        <v>31</v>
       </c>
       <c r="B305" t="n">
-        <v>236</v>
+        <v>90</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="B306" t="n">
-        <v>209</v>
+        <v>108</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>115</v>
+        <v>225</v>
       </c>
       <c r="B307" t="n">
-        <v>113</v>
+        <v>190</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>86</v>
+        <v>181</v>
       </c>
       <c r="B308" t="n">
-        <v>201</v>
+        <v>63</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>212</v>
+        <v>144</v>
       </c>
       <c r="B309" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="B310" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>115</v>
+        <v>233</v>
       </c>
       <c r="B311" t="n">
-        <v>193</v>
+        <v>90</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="B312" t="n">
-        <v>166</v>
+        <v>62</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="B313" t="n">
-        <v>38</v>
+        <v>230</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="B314" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>241</v>
+        <v>127</v>
       </c>
       <c r="B315" t="n">
-        <v>217</v>
+        <v>52</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B316" t="n">
-        <v>124</v>
+        <v>76</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>8</v>
+        <v>84</v>
       </c>
       <c r="B317" t="n">
-        <v>85</v>
+        <v>208</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>4</v>
+        <v>249</v>
       </c>
       <c r="B318" t="n">
-        <v>254</v>
+        <v>24</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>67</v>
+        <v>170</v>
       </c>
       <c r="B319" t="n">
-        <v>188</v>
+        <v>132</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>225</v>
+        <v>28</v>
       </c>
       <c r="B320" t="n">
-        <v>5</v>
+        <v>189</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>207</v>
+        <v>138</v>
       </c>
       <c r="B321" t="n">
-        <v>202</v>
+        <v>108</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>184</v>
+        <v>154</v>
       </c>
       <c r="B322" t="n">
-        <v>28</v>
+        <v>95</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>73</v>
+        <v>202</v>
       </c>
       <c r="B323" t="n">
-        <v>180</v>
+        <v>52</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>177</v>
+        <v>8</v>
       </c>
       <c r="B324" t="n">
-        <v>87</v>
+        <v>130</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="B325" t="n">
-        <v>74</v>
+        <v>142</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>250</v>
+        <v>145</v>
       </c>
       <c r="B326" t="n">
-        <v>138</v>
+        <v>67</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>154</v>
+        <v>227</v>
       </c>
       <c r="B327" t="n">
-        <v>102</v>
+        <v>49</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="B328" t="n">
-        <v>128</v>
+        <v>23</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>159</v>
+        <v>31</v>
       </c>
       <c r="B329" t="n">
-        <v>192</v>
+        <v>57</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>164</v>
+        <v>45</v>
       </c>
       <c r="B330" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="B331" t="n">
-        <v>90</v>
+        <v>195</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>21</v>
+        <v>233</v>
       </c>
       <c r="B332" t="n">
-        <v>155</v>
+        <v>50</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B333" t="n">
-        <v>5</v>
+        <v>216</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="B334" t="n">
-        <v>83</v>
+        <v>137</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>37</v>
+        <v>170</v>
       </c>
       <c r="B335" t="n">
-        <v>163</v>
+        <v>155</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>129</v>
+        <v>248</v>
       </c>
       <c r="B336" t="n">
-        <v>33</v>
+        <v>244</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>230</v>
+        <v>136</v>
       </c>
       <c r="B337" t="n">
-        <v>22</v>
+        <v>71</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>255</v>
+        <v>12</v>
       </c>
       <c r="B338" t="n">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="B339" t="n">
-        <v>25</v>
+        <v>119</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>225</v>
+        <v>158</v>
       </c>
       <c r="B340" t="n">
-        <v>108</v>
+        <v>59</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>125</v>
+        <v>21</v>
       </c>
       <c r="B341" t="n">
-        <v>217</v>
+        <v>44</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>186</v>
+        <v>142</v>
       </c>
       <c r="B342" t="n">
-        <v>227</v>
+        <v>45</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="B343" t="n">
-        <v>139</v>
+        <v>189</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="B344" t="n">
-        <v>101</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>219</v>
+        <v>93</v>
       </c>
       <c r="B345" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="B346" t="n">
-        <v>210</v>
+        <v>250</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="B347" t="n">
-        <v>107</v>
+        <v>193</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="B348" t="n">
-        <v>237</v>
+        <v>150</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>141</v>
+        <v>24</v>
       </c>
       <c r="B349" t="n">
-        <v>83</v>
+        <v>65</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="B350" t="n">
-        <v>250</v>
+        <v>112</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B351" t="n">
-        <v>138</v>
+        <v>37</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>183</v>
+        <v>238</v>
       </c>
       <c r="B352" t="n">
-        <v>198</v>
+        <v>172</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="B353" t="n">
-        <v>5</v>
+        <v>183</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>44</v>
+        <v>153</v>
       </c>
       <c r="B354" t="n">
-        <v>236</v>
+        <v>11</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>192</v>
+        <v>110</v>
       </c>
       <c r="B355" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>118</v>
+        <v>245</v>
       </c>
       <c r="B356" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>222</v>
+        <v>51</v>
       </c>
       <c r="B357" t="n">
-        <v>124</v>
+        <v>197</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>145</v>
+        <v>70</v>
       </c>
       <c r="B358" t="n">
-        <v>162</v>
+        <v>206</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>158</v>
+        <v>228</v>
       </c>
       <c r="B359" t="n">
-        <v>75</v>
+        <v>14</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>177</v>
+        <v>219</v>
       </c>
       <c r="B360" t="n">
-        <v>251</v>
+        <v>70</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>91</v>
+        <v>241</v>
       </c>
       <c r="B361" t="n">
-        <v>212</v>
+        <v>234</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>152</v>
+        <v>252</v>
       </c>
       <c r="B362" t="n">
-        <v>42</v>
+        <v>247</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>163</v>
+        <v>242</v>
       </c>
       <c r="B363" t="n">
-        <v>242</v>
+        <v>231</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>17</v>
+        <v>149</v>
       </c>
       <c r="B364" t="n">
-        <v>135</v>
+        <v>151</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>208</v>
+        <v>17</v>
       </c>
       <c r="B365" t="n">
-        <v>46</v>
+        <v>155</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B366" t="n">
-        <v>190</v>
+        <v>201</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>190</v>
+        <v>127</v>
       </c>
       <c r="B367" t="n">
-        <v>248</v>
+        <v>101</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="B368" t="n">
-        <v>132</v>
+        <v>58</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="B369" t="n">
-        <v>92</v>
+        <v>253</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="B370" t="n">
-        <v>147</v>
+        <v>138</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="B371" t="n">
-        <v>254</v>
+        <v>111</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>24</v>
+        <v>232</v>
       </c>
       <c r="B372" t="n">
-        <v>40</v>
+        <v>240</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B373" t="n">
-        <v>93</v>
+        <v>206</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>75</v>
+        <v>155</v>
       </c>
       <c r="B374" t="n">
-        <v>131</v>
+        <v>230</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="B375" t="n">
-        <v>10</v>
+        <v>145</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B376" t="n">
-        <v>120</v>
+        <v>76</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>117</v>
+        <v>54</v>
       </c>
       <c r="B377" t="n">
-        <v>104</v>
+        <v>80</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>238</v>
+        <v>39</v>
       </c>
       <c r="B378" t="n">
-        <v>93</v>
+        <v>252</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>132</v>
+        <v>24</v>
       </c>
       <c r="B379" t="n">
-        <v>35</v>
+        <v>157</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>45</v>
+        <v>227</v>
       </c>
       <c r="B380" t="n">
-        <v>184</v>
+        <v>255</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>16</v>
+        <v>143</v>
       </c>
       <c r="B381" t="n">
-        <v>147</v>
+        <v>60</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>123</v>
+        <v>185</v>
       </c>
       <c r="B382" t="n">
-        <v>7</v>
+        <v>209</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="B383" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="B384" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>64</v>
+        <v>144</v>
       </c>
       <c r="B385" t="n">
-        <v>95</v>
+        <v>243</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>185</v>
+        <v>21</v>
       </c>
       <c r="B386" t="n">
-        <v>218</v>
+        <v>206</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B387" t="n">
-        <v>149</v>
+        <v>184</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>102</v>
+        <v>181</v>
       </c>
       <c r="B388" t="n">
-        <v>193</v>
+        <v>136</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>247</v>
+        <v>116</v>
       </c>
       <c r="B389" t="n">
-        <v>93</v>
+        <v>74</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>71</v>
+        <v>173</v>
       </c>
       <c r="B390" t="n">
-        <v>5</v>
+        <v>246</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="B391" t="n">
-        <v>67</v>
+        <v>170</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>201</v>
+        <v>146</v>
       </c>
       <c r="B392" t="n">
-        <v>13</v>
+        <v>77</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>151</v>
+        <v>31</v>
       </c>
       <c r="B393" t="n">
-        <v>178</v>
+        <v>134</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="B394" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="B395" t="n">
-        <v>213</v>
+        <v>137</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>23</v>
+        <v>233</v>
       </c>
       <c r="B396" t="n">
-        <v>170</v>
+        <v>236</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>168</v>
+        <v>49</v>
       </c>
       <c r="B397" t="n">
-        <v>193</v>
+        <v>0</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>243</v>
+        <v>109</v>
       </c>
       <c r="B398" t="n">
-        <v>172</v>
+        <v>139</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>207</v>
+        <v>50</v>
       </c>
       <c r="B399" t="n">
-        <v>113</v>
+        <v>202</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>49</v>
+        <v>226</v>
       </c>
       <c r="B400" t="n">
-        <v>243</v>
+        <v>12</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>237</v>
+        <v>54</v>
       </c>
       <c r="B401" t="n">
-        <v>71</v>
+        <v>236</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>156</v>
+        <v>100</v>
       </c>
       <c r="B402" t="n">
-        <v>214</v>
+        <v>129</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>207</v>
+        <v>109</v>
       </c>
       <c r="B403" t="n">
-        <v>108</v>
+        <v>136</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>201</v>
+        <v>119</v>
       </c>
       <c r="B404" t="n">
-        <v>128</v>
+        <v>212</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>207</v>
+        <v>127</v>
       </c>
       <c r="B405" t="n">
-        <v>86</v>
+        <v>189</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="B406" t="n">
-        <v>74</v>
+        <v>32</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>11</v>
+        <v>145</v>
       </c>
       <c r="B407" t="n">
-        <v>125</v>
+        <v>4</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>121</v>
+        <v>49</v>
       </c>
       <c r="B408" t="n">
-        <v>154</v>
+        <v>230</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="B409" t="n">
-        <v>115</v>
+        <v>150</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="B410" t="n">
-        <v>171</v>
+        <v>80</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>43</v>
+        <v>183</v>
       </c>
       <c r="B411" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>237</v>
+        <v>145</v>
       </c>
       <c r="B412" t="n">
-        <v>188</v>
+        <v>173</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>183</v>
+        <v>74</v>
       </c>
       <c r="B413" t="n">
-        <v>98</v>
+        <v>205</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>146</v>
+        <v>42</v>
       </c>
       <c r="B414" t="n">
-        <v>17</v>
+        <v>176</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="B415" t="n">
-        <v>80</v>
+        <v>149</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="B416" t="n">
-        <v>37</v>
+        <v>92</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>253</v>
+        <v>130</v>
       </c>
       <c r="B417" t="n">
-        <v>240</v>
+        <v>46</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="B418" t="n">
-        <v>209</v>
+        <v>84</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>188</v>
+        <v>59</v>
       </c>
       <c r="B419" t="n">
-        <v>219</v>
+        <v>48</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>68</v>
+        <v>172</v>
       </c>
       <c r="B420" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>123</v>
+        <v>188</v>
       </c>
       <c r="B421" t="n">
-        <v>255</v>
+        <v>3</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>58</v>
+        <v>183</v>
       </c>
       <c r="B422" t="n">
-        <v>233</v>
+        <v>136</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>70</v>
+        <v>211</v>
       </c>
       <c r="B423" t="n">
-        <v>221</v>
+        <v>35</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>110</v>
+        <v>156</v>
       </c>
       <c r="B424" t="n">
-        <v>90</v>
+        <v>25</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>99</v>
+        <v>236</v>
       </c>
       <c r="B425" t="n">
-        <v>80</v>
+        <v>185</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="B426" t="n">
-        <v>93</v>
+        <v>163</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="B427" t="n">
-        <v>65</v>
+        <v>155</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="B428" t="n">
-        <v>173</v>
+        <v>19</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B429" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>176</v>
+        <v>86</v>
       </c>
       <c r="B430" t="n">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>8</v>
+        <v>224</v>
       </c>
       <c r="B431" t="n">
-        <v>111</v>
+        <v>151</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>114</v>
+        <v>193</v>
       </c>
       <c r="B432" t="n">
-        <v>149</v>
+        <v>46</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="B433" t="n">
-        <v>70</v>
+        <v>105</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="B434" t="n">
-        <v>124</v>
+        <v>153</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>154</v>
+        <v>8</v>
       </c>
       <c r="B435" t="n">
-        <v>156</v>
+        <v>30</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="B436" t="n">
-        <v>209</v>
+        <v>122</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>166</v>
+        <v>192</v>
       </c>
       <c r="B437" t="n">
-        <v>134</v>
+        <v>112</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B438" t="n">
-        <v>247</v>
+        <v>24</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="B439" t="n">
-        <v>250</v>
+        <v>45</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>185</v>
+        <v>23</v>
       </c>
       <c r="B440" t="n">
-        <v>55</v>
+        <v>241</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c r="B441" t="n">
-        <v>186</v>
+        <v>145</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>135</v>
+        <v>84</v>
       </c>
       <c r="B442" t="n">
-        <v>190</v>
+        <v>50</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="B443" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B444" t="n">
-        <v>144</v>
+        <v>253</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>249</v>
+        <v>184</v>
       </c>
       <c r="B445" t="n">
-        <v>75</v>
+        <v>108</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>229</v>
+        <v>59</v>
       </c>
       <c r="B446" t="n">
-        <v>95</v>
+        <v>186</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>236</v>
+        <v>110</v>
       </c>
       <c r="B447" t="n">
-        <v>146</v>
+        <v>230</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="B448" t="n">
-        <v>26</v>
+        <v>164</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>142</v>
+        <v>218</v>
       </c>
       <c r="B449" t="n">
-        <v>60</v>
+        <v>210</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>48</v>
+        <v>203</v>
       </c>
       <c r="B450" t="n">
-        <v>19</v>
+        <v>182</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>17</v>
+        <v>204</v>
       </c>
       <c r="B451" t="n">
-        <v>241</v>
+        <v>76</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>242</v>
+        <v>114</v>
       </c>
       <c r="B452" t="n">
-        <v>126</v>
+        <v>57</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="B453" t="n">
-        <v>142</v>
+        <v>106</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="B454" t="n">
-        <v>100</v>
+        <v>11</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="B455" t="n">
-        <v>148</v>
+        <v>128</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B456" t="n">
-        <v>239</v>
+        <v>136</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>126</v>
+        <v>209</v>
       </c>
       <c r="B457" t="n">
-        <v>28</v>
+        <v>62</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="B458" t="n">
-        <v>180</v>
+        <v>143</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="B459" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>100</v>
+        <v>243</v>
       </c>
       <c r="B460" t="n">
-        <v>68</v>
+        <v>199</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="B461" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="B462" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>245</v>
+        <v>152</v>
       </c>
       <c r="B463" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="B464" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>244</v>
+        <v>155</v>
       </c>
       <c r="B465" t="n">
-        <v>87</v>
+        <v>71</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>3</v>
+        <v>206</v>
       </c>
       <c r="B466" t="n">
-        <v>49</v>
+        <v>114</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>133</v>
+        <v>183</v>
       </c>
       <c r="B467" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B468" t="n">
-        <v>185</v>
+        <v>141</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>242</v>
+        <v>32</v>
       </c>
       <c r="B469" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>50</v>
+        <v>141</v>
       </c>
       <c r="B470" t="n">
-        <v>48</v>
+        <v>117</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="B471" t="n">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>13</v>
+        <v>220</v>
       </c>
       <c r="B472" t="n">
-        <v>75</v>
+        <v>58</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>243</v>
+        <v>23</v>
       </c>
       <c r="B473" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>93</v>
+        <v>223</v>
       </c>
       <c r="B474" t="n">
-        <v>131</v>
+        <v>223</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>89</v>
+        <v>207</v>
       </c>
       <c r="B475" t="n">
-        <v>161</v>
+        <v>91</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="B476" t="n">
-        <v>183</v>
+        <v>22</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>176</v>
+        <v>99</v>
       </c>
       <c r="B477" t="n">
-        <v>241</v>
+        <v>76</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="B478" t="n">
-        <v>235</v>
+        <v>35</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>208</v>
+        <v>100</v>
       </c>
       <c r="B479" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="B480" t="n">
-        <v>204</v>
+        <v>251</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>79</v>
+        <v>214</v>
       </c>
       <c r="B481" t="n">
-        <v>161</v>
+        <v>8</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>75</v>
+        <v>235</v>
       </c>
       <c r="B482" t="n">
-        <v>229</v>
+        <v>82</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="B483" t="n">
-        <v>151</v>
+        <v>2</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="B484" t="n">
-        <v>68</v>
+        <v>187</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="B485" t="n">
-        <v>139</v>
+        <v>185</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="B486" t="n">
-        <v>251</v>
+        <v>214</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="B487" t="n">
-        <v>248</v>
+        <v>254</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>180</v>
+        <v>61</v>
       </c>
       <c r="B488" t="n">
-        <v>37</v>
+        <v>116</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="B489" t="n">
-        <v>112</v>
+        <v>174</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="B490" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="B491" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>107</v>
+        <v>150</v>
       </c>
       <c r="B492" t="n">
-        <v>32</v>
+        <v>126</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="B493" t="n">
-        <v>79</v>
+        <v>200</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="B494" t="n">
-        <v>6</v>
+        <v>145</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>222</v>
+        <v>23</v>
       </c>
       <c r="B495" t="n">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>205</v>
+        <v>16</v>
       </c>
       <c r="B496" t="n">
-        <v>69</v>
+        <v>52</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>108</v>
+        <v>233</v>
       </c>
       <c r="B497" t="n">
-        <v>80</v>
+        <v>104</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="B498" t="n">
-        <v>219</v>
+        <v>132</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B499" t="n">
-        <v>168</v>
+        <v>215</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>218</v>
+        <v>146</v>
       </c>
       <c r="B500" t="n">
-        <v>65</v>
+        <v>188</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>9</v>
+        <v>209</v>
       </c>
       <c r="B501" t="n">
-        <v>176</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -4614,10 +4614,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.62082</v>
+        <v>7.56732</v>
       </c>
       <c r="C3" t="n">
-        <v>7.59171</v>
+        <v>7.57079</v>
       </c>
     </row>
     <row r="4">
@@ -4627,10 +4627,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>219.872</v>
+        <v>276.192</v>
       </c>
       <c r="C4" t="n">
-        <v>250.592</v>
+        <v>264.928</v>
       </c>
     </row>
   </sheetData>
@@ -4669,10 +4669,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -4680,10 +4680,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -4691,10 +4691,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -4705,7 +4705,7 @@
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -4716,7 +4716,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -4724,10 +4724,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -4735,10 +4735,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4746,10 +4746,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -4757,10 +4757,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -4771,7 +4771,7 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -4779,10 +4779,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
         <v>4</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -4790,10 +4790,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -4801,10 +4801,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -4812,10 +4812,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4823,10 +4823,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -4837,7 +4837,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -4856,10 +4856,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -4870,7 +4870,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -4878,10 +4878,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -4889,7 +4889,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
@@ -4900,10 +4900,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -4911,10 +4911,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -4922,10 +4922,10 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -4933,10 +4933,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -4947,7 +4947,7 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -4955,7 +4955,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
@@ -4969,7 +4969,7 @@
         <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -4977,10 +4977,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -4988,10 +4988,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -4999,10 +4999,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -5010,10 +5010,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -5021,10 +5021,10 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -5043,10 +5043,10 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -5054,7 +5054,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
         <v>2</v>
@@ -5065,10 +5065,10 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -5079,7 +5079,7 @@
         <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -5090,7 +5090,7 @@
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -5098,10 +5098,10 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -5109,7 +5109,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
         <v>2</v>
@@ -5131,10 +5131,10 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -5142,10 +5142,10 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -5153,7 +5153,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C46" t="n">
         <v>3</v>
@@ -5164,7 +5164,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C47" t="n">
         <v>2</v>
@@ -5175,10 +5175,10 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -5186,10 +5186,10 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -5197,10 +5197,10 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -5211,7 +5211,7 @@
         <v>2</v>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -5219,10 +5219,10 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -5233,7 +5233,7 @@
         <v>2</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -5241,10 +5241,10 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -5255,7 +5255,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -5263,10 +5263,10 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C56" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -5274,10 +5274,10 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -5285,10 +5285,10 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -5296,10 +5296,10 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60">
@@ -5307,10 +5307,10 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61">
@@ -5318,10 +5318,10 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -5329,7 +5329,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62" t="n">
         <v>4</v>
@@ -5340,10 +5340,10 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -5351,7 +5351,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C64" t="n">
         <v>3</v>
@@ -5362,7 +5362,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C65" t="n">
         <v>2</v>
@@ -5373,10 +5373,10 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -5384,10 +5384,10 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -5398,7 +5398,7 @@
         <v>2</v>
       </c>
       <c r="C68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -5406,10 +5406,10 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -5417,10 +5417,10 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -5428,10 +5428,10 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -5439,10 +5439,10 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -5450,10 +5450,10 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -5461,10 +5461,10 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -5472,7 +5472,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
@@ -5483,10 +5483,10 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -5494,10 +5494,10 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C77" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -5505,10 +5505,10 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
@@ -5519,7 +5519,7 @@
         <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -5527,10 +5527,10 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -5541,7 +5541,7 @@
         <v>2</v>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -5549,7 +5549,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C82" t="n">
         <v>4</v>
@@ -5560,10 +5560,10 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C83" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -5571,10 +5571,10 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -5582,10 +5582,10 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -5593,10 +5593,10 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -5604,10 +5604,10 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C87" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -5615,10 +5615,10 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
@@ -5626,10 +5626,10 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -5637,7 +5637,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C90" t="n">
         <v>1</v>
@@ -5651,7 +5651,7 @@
         <v>3</v>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -5659,10 +5659,10 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
@@ -5670,10 +5670,10 @@
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -5681,10 +5681,10 @@
         <v>92</v>
       </c>
       <c r="B94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -5695,7 +5695,7 @@
         <v>2</v>
       </c>
       <c r="C95" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -5703,7 +5703,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C96" t="n">
         <v>1</v>
@@ -5714,10 +5714,10 @@
         <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
@@ -5725,10 +5725,10 @@
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -5736,7 +5736,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
@@ -5747,10 +5747,10 @@
         <v>98</v>
       </c>
       <c r="B100" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C100" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -5761,7 +5761,7 @@
         <v>2</v>
       </c>
       <c r="C101" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -5769,10 +5769,10 @@
         <v>100</v>
       </c>
       <c r="B102" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C102" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -5780,10 +5780,10 @@
         <v>101</v>
       </c>
       <c r="B103" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -5791,10 +5791,10 @@
         <v>102</v>
       </c>
       <c r="B104" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -5802,10 +5802,10 @@
         <v>103</v>
       </c>
       <c r="B105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -5813,7 +5813,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C106" t="n">
         <v>1</v>
@@ -5824,7 +5824,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C107" t="n">
         <v>1</v>
@@ -5835,7 +5835,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C108" t="n">
         <v>4</v>
@@ -5846,10 +5846,10 @@
         <v>107</v>
       </c>
       <c r="B109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C109" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -5857,10 +5857,10 @@
         <v>108</v>
       </c>
       <c r="B110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C110" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111">
@@ -5868,7 +5868,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
@@ -5879,10 +5879,10 @@
         <v>110</v>
       </c>
       <c r="B112" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C112" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -5890,10 +5890,10 @@
         <v>111</v>
       </c>
       <c r="B113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -5901,10 +5901,10 @@
         <v>112</v>
       </c>
       <c r="B114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C114" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115">
@@ -5912,7 +5912,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C115" t="n">
         <v>2</v>
@@ -5923,7 +5923,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C116" t="n">
         <v>2</v>
@@ -5934,10 +5934,10 @@
         <v>115</v>
       </c>
       <c r="B117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -5945,10 +5945,10 @@
         <v>116</v>
       </c>
       <c r="B118" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119">
@@ -5956,10 +5956,10 @@
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C119" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120">
@@ -5967,10 +5967,10 @@
         <v>118</v>
       </c>
       <c r="B120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121">
@@ -5978,10 +5978,10 @@
         <v>119</v>
       </c>
       <c r="B121" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
@@ -5992,7 +5992,7 @@
         <v>2</v>
       </c>
       <c r="C122" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
@@ -6000,10 +6000,10 @@
         <v>121</v>
       </c>
       <c r="B123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -6011,7 +6011,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C124" t="n">
         <v>1</v>
@@ -6022,10 +6022,10 @@
         <v>123</v>
       </c>
       <c r="B125" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
@@ -6033,10 +6033,10 @@
         <v>124</v>
       </c>
       <c r="B126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
@@ -6044,7 +6044,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C127" t="n">
         <v>1</v>
@@ -6055,10 +6055,10 @@
         <v>126</v>
       </c>
       <c r="B128" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C128" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
@@ -6066,7 +6066,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C129" t="n">
         <v>1</v>
@@ -6077,10 +6077,10 @@
         <v>128</v>
       </c>
       <c r="B130" t="n">
+        <v>1</v>
+      </c>
+      <c r="C130" t="n">
         <v>4</v>
-      </c>
-      <c r="C130" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -6088,10 +6088,10 @@
         <v>129</v>
       </c>
       <c r="B131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
@@ -6099,10 +6099,10 @@
         <v>130</v>
       </c>
       <c r="B132" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C132" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -6110,10 +6110,10 @@
         <v>131</v>
       </c>
       <c r="B133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -6121,10 +6121,10 @@
         <v>132</v>
       </c>
       <c r="B134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
@@ -6132,7 +6132,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C135" t="n">
         <v>1</v>
@@ -6143,7 +6143,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C136" t="n">
         <v>2</v>
@@ -6154,10 +6154,10 @@
         <v>135</v>
       </c>
       <c r="B137" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -6165,10 +6165,10 @@
         <v>136</v>
       </c>
       <c r="B138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C138" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="139">
@@ -6176,10 +6176,10 @@
         <v>137</v>
       </c>
       <c r="B139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C139" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140">
@@ -6187,10 +6187,10 @@
         <v>138</v>
       </c>
       <c r="B140" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
@@ -6201,7 +6201,7 @@
         <v>2</v>
       </c>
       <c r="C141" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="142">
@@ -6209,10 +6209,10 @@
         <v>140</v>
       </c>
       <c r="B142" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C142" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -6220,7 +6220,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C143" t="n">
         <v>1</v>
@@ -6231,10 +6231,10 @@
         <v>142</v>
       </c>
       <c r="B144" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C144" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
@@ -6242,10 +6242,10 @@
         <v>143</v>
       </c>
       <c r="B145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -6253,10 +6253,10 @@
         <v>144</v>
       </c>
       <c r="B146" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -6264,10 +6264,10 @@
         <v>145</v>
       </c>
       <c r="B147" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C147" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148">
@@ -6275,10 +6275,10 @@
         <v>146</v>
       </c>
       <c r="B148" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -6286,10 +6286,10 @@
         <v>147</v>
       </c>
       <c r="B149" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C149" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -6297,7 +6297,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C150" t="n">
         <v>1</v>
@@ -6308,7 +6308,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C151" t="n">
         <v>3</v>
@@ -6319,10 +6319,10 @@
         <v>150</v>
       </c>
       <c r="B152" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C152" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="153">
@@ -6330,10 +6330,10 @@
         <v>151</v>
       </c>
       <c r="B153" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C153" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154">
@@ -6341,10 +6341,10 @@
         <v>152</v>
       </c>
       <c r="B154" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C154" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -6355,7 +6355,7 @@
         <v>1</v>
       </c>
       <c r="C155" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="156">
@@ -6363,10 +6363,10 @@
         <v>154</v>
       </c>
       <c r="B156" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157">
@@ -6374,10 +6374,10 @@
         <v>155</v>
       </c>
       <c r="B157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C157" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="158">
@@ -6385,10 +6385,10 @@
         <v>156</v>
       </c>
       <c r="B158" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159">
@@ -6396,10 +6396,10 @@
         <v>157</v>
       </c>
       <c r="B159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -6407,10 +6407,10 @@
         <v>158</v>
       </c>
       <c r="B160" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -6418,7 +6418,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C161" t="n">
         <v>1</v>
@@ -6429,10 +6429,10 @@
         <v>160</v>
       </c>
       <c r="B162" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -6440,10 +6440,10 @@
         <v>161</v>
       </c>
       <c r="B163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C163" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -6451,10 +6451,10 @@
         <v>162</v>
       </c>
       <c r="B164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C164" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
@@ -6462,10 +6462,10 @@
         <v>163</v>
       </c>
       <c r="B165" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C165" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166">
@@ -6473,10 +6473,10 @@
         <v>164</v>
       </c>
       <c r="B166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C166" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167">
@@ -6484,10 +6484,10 @@
         <v>165</v>
       </c>
       <c r="B167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="168">
@@ -6495,10 +6495,10 @@
         <v>166</v>
       </c>
       <c r="B168" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C168" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="169">
@@ -6506,7 +6506,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C169" t="n">
         <v>1</v>
@@ -6517,10 +6517,10 @@
         <v>168</v>
       </c>
       <c r="B170" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C170" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171">
@@ -6528,7 +6528,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C171" t="n">
         <v>1</v>
@@ -6539,10 +6539,10 @@
         <v>170</v>
       </c>
       <c r="B172" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C172" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="173">
@@ -6550,10 +6550,10 @@
         <v>171</v>
       </c>
       <c r="B173" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -6561,10 +6561,10 @@
         <v>172</v>
       </c>
       <c r="B174" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -6572,10 +6572,10 @@
         <v>173</v>
       </c>
       <c r="B175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C175" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -6583,10 +6583,10 @@
         <v>174</v>
       </c>
       <c r="B176" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C176" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -6594,10 +6594,10 @@
         <v>175</v>
       </c>
       <c r="B177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -6608,7 +6608,7 @@
         <v>3</v>
       </c>
       <c r="C178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
@@ -6616,10 +6616,10 @@
         <v>177</v>
       </c>
       <c r="B179" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C179" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180">
@@ -6630,7 +6630,7 @@
         <v>1</v>
       </c>
       <c r="C180" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181">
@@ -6638,10 +6638,10 @@
         <v>179</v>
       </c>
       <c r="B181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -6649,10 +6649,10 @@
         <v>180</v>
       </c>
       <c r="B182" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C182" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -6674,7 +6674,7 @@
         <v>1</v>
       </c>
       <c r="C184" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -6682,7 +6682,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C185" t="n">
         <v>2</v>
@@ -6696,7 +6696,7 @@
         <v>1</v>
       </c>
       <c r="C186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
@@ -6704,10 +6704,10 @@
         <v>185</v>
       </c>
       <c r="B187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C187" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188">
@@ -6715,10 +6715,10 @@
         <v>186</v>
       </c>
       <c r="B188" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C188" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="189">
@@ -6729,7 +6729,7 @@
         <v>1</v>
       </c>
       <c r="C189" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190">
@@ -6748,10 +6748,10 @@
         <v>189</v>
       </c>
       <c r="B191" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C191" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="192">
@@ -6759,10 +6759,10 @@
         <v>190</v>
       </c>
       <c r="B192" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C192" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="193">
@@ -6770,10 +6770,10 @@
         <v>191</v>
       </c>
       <c r="B193" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C193" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="194">
@@ -6781,7 +6781,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C194" t="n">
         <v>1</v>
@@ -6795,7 +6795,7 @@
         <v>4</v>
       </c>
       <c r="C195" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="196">
@@ -6806,7 +6806,7 @@
         <v>2</v>
       </c>
       <c r="C196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -6814,10 +6814,10 @@
         <v>195</v>
       </c>
       <c r="B197" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C197" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198">
@@ -6825,10 +6825,10 @@
         <v>196</v>
       </c>
       <c r="B198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -6836,7 +6836,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C199" t="n">
         <v>1</v>
@@ -6850,7 +6850,7 @@
         <v>2</v>
       </c>
       <c r="C200" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
@@ -6858,10 +6858,10 @@
         <v>199</v>
       </c>
       <c r="B201" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C201" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="202">
@@ -6869,7 +6869,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C202" t="n">
         <v>2</v>
@@ -6880,7 +6880,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C203" t="n">
         <v>3</v>
@@ -6891,10 +6891,10 @@
         <v>202</v>
       </c>
       <c r="B204" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C204" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
@@ -6902,10 +6902,10 @@
         <v>203</v>
       </c>
       <c r="B205" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206">
@@ -6916,7 +6916,7 @@
         <v>1</v>
       </c>
       <c r="C206" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207">
@@ -6924,10 +6924,10 @@
         <v>205</v>
       </c>
       <c r="B207" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208">
@@ -6938,7 +6938,7 @@
         <v>3</v>
       </c>
       <c r="C208" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="209">
@@ -6946,10 +6946,10 @@
         <v>207</v>
       </c>
       <c r="B209" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C209" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="210">
@@ -6957,10 +6957,10 @@
         <v>208</v>
       </c>
       <c r="B210" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211">
@@ -6968,10 +6968,10 @@
         <v>209</v>
       </c>
       <c r="B211" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C211" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212">
@@ -6982,7 +6982,7 @@
         <v>1</v>
       </c>
       <c r="C212" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="213">
@@ -6990,10 +6990,10 @@
         <v>211</v>
       </c>
       <c r="B213" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C213" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="214">
@@ -7001,10 +7001,10 @@
         <v>212</v>
       </c>
       <c r="B214" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C214" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215">
@@ -7012,10 +7012,10 @@
         <v>213</v>
       </c>
       <c r="B215" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C215" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216">
@@ -7034,10 +7034,10 @@
         <v>215</v>
       </c>
       <c r="B217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C217" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="218">
@@ -7056,10 +7056,10 @@
         <v>217</v>
       </c>
       <c r="B219" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C219" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="220">
@@ -7067,10 +7067,10 @@
         <v>218</v>
       </c>
       <c r="B220" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C220" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221">
@@ -7078,10 +7078,10 @@
         <v>219</v>
       </c>
       <c r="B221" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C221" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -7092,7 +7092,7 @@
         <v>1</v>
       </c>
       <c r="C222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223">
@@ -7100,10 +7100,10 @@
         <v>221</v>
       </c>
       <c r="B223" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C223" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
@@ -7114,7 +7114,7 @@
         <v>2</v>
       </c>
       <c r="C224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225">
@@ -7125,7 +7125,7 @@
         <v>2</v>
       </c>
       <c r="C225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226">
@@ -7133,10 +7133,10 @@
         <v>224</v>
       </c>
       <c r="B226" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C226" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227">
@@ -7144,7 +7144,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C227" t="n">
         <v>2</v>
@@ -7155,7 +7155,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C228" t="n">
         <v>2</v>
@@ -7166,10 +7166,10 @@
         <v>227</v>
       </c>
       <c r="B229" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="230">
@@ -7188,10 +7188,10 @@
         <v>229</v>
       </c>
       <c r="B231" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C231" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="232">
@@ -7199,10 +7199,10 @@
         <v>230</v>
       </c>
       <c r="B232" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C232" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="233">
@@ -7210,10 +7210,10 @@
         <v>231</v>
       </c>
       <c r="B233" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C233" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">
@@ -7221,10 +7221,10 @@
         <v>232</v>
       </c>
       <c r="B234" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C234" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235">
@@ -7232,10 +7232,10 @@
         <v>233</v>
       </c>
       <c r="B235" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C235" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236">
@@ -7243,7 +7243,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C236" t="n">
         <v>1</v>
@@ -7254,10 +7254,10 @@
         <v>235</v>
       </c>
       <c r="B237" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="238">
@@ -7265,10 +7265,10 @@
         <v>236</v>
       </c>
       <c r="B238" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C238" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="239">
@@ -7276,10 +7276,10 @@
         <v>237</v>
       </c>
       <c r="B239" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240">
@@ -7290,7 +7290,7 @@
         <v>3</v>
       </c>
       <c r="C240" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
@@ -7301,7 +7301,7 @@
         <v>1</v>
       </c>
       <c r="C241" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
@@ -7309,10 +7309,10 @@
         <v>240</v>
       </c>
       <c r="B242" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C242" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="243">
@@ -7323,7 +7323,7 @@
         <v>2</v>
       </c>
       <c r="C243" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244">
@@ -7331,7 +7331,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C244" t="n">
         <v>1</v>
@@ -7342,10 +7342,10 @@
         <v>243</v>
       </c>
       <c r="B245" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="246">
@@ -7353,10 +7353,10 @@
         <v>244</v>
       </c>
       <c r="B246" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C246" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="247">
@@ -7364,10 +7364,10 @@
         <v>245</v>
       </c>
       <c r="B247" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C247" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="248">
@@ -7375,10 +7375,10 @@
         <v>246</v>
       </c>
       <c r="B248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C248" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="249">
@@ -7389,7 +7389,7 @@
         <v>2</v>
       </c>
       <c r="C249" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
@@ -7397,10 +7397,10 @@
         <v>248</v>
       </c>
       <c r="B250" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C250" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
@@ -7408,10 +7408,10 @@
         <v>249</v>
       </c>
       <c r="B251" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C251" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
@@ -7419,7 +7419,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C252" t="n">
         <v>2</v>
@@ -7430,10 +7430,10 @@
         <v>251</v>
       </c>
       <c r="B253" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C253" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -7452,10 +7452,10 @@
         <v>253</v>
       </c>
       <c r="B255" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -7463,7 +7463,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C256" t="n">
         <v>3</v>
@@ -7474,7 +7474,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C257" t="n">
         <v>1</v>
